--- a/plantilla_computadores.xlsx
+++ b/plantilla_computadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DatosFtp\Desarrollos\SIAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7458DA18-D748-4940-8232-0098E2C2CCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BDAFAA-89FE-403D-B9CF-D43EBE7DFAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="plantilla_computadores" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4961" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5511" uniqueCount="1108">
   <si>
     <t>Codigo Inventario</t>
   </si>
@@ -1706,7 +1706,1657 @@
     <t>Arriendo</t>
   </si>
   <si>
-    <t>Prchile</t>
+    <t>Nombre Equipo</t>
+  </si>
+  <si>
+    <t>Prchile-35097</t>
+  </si>
+  <si>
+    <t>Prchile-35098</t>
+  </si>
+  <si>
+    <t>Prchile-35099</t>
+  </si>
+  <si>
+    <t>Prchile-35100</t>
+  </si>
+  <si>
+    <t>Prchile-35101</t>
+  </si>
+  <si>
+    <t>Prchile-35102</t>
+  </si>
+  <si>
+    <t>Prchile-35103</t>
+  </si>
+  <si>
+    <t>Prchile-35104</t>
+  </si>
+  <si>
+    <t>Prchile-35105</t>
+  </si>
+  <si>
+    <t>Prchile-35106</t>
+  </si>
+  <si>
+    <t>Prchile-35107</t>
+  </si>
+  <si>
+    <t>Prchile-35108</t>
+  </si>
+  <si>
+    <t>Prchile-35109</t>
+  </si>
+  <si>
+    <t>Prchile-35110</t>
+  </si>
+  <si>
+    <t>Prchile-35111</t>
+  </si>
+  <si>
+    <t>Prchile-35112</t>
+  </si>
+  <si>
+    <t>Prchile-35113</t>
+  </si>
+  <si>
+    <t>Prchile-35114</t>
+  </si>
+  <si>
+    <t>Prchile-35115</t>
+  </si>
+  <si>
+    <t>Prchile-35116</t>
+  </si>
+  <si>
+    <t>Prchile-35117</t>
+  </si>
+  <si>
+    <t>Prchile-35118</t>
+  </si>
+  <si>
+    <t>Prchile-35119</t>
+  </si>
+  <si>
+    <t>Prchile-35120</t>
+  </si>
+  <si>
+    <t>Prchile-35121</t>
+  </si>
+  <si>
+    <t>Prchile-35122</t>
+  </si>
+  <si>
+    <t>Prchile-35123</t>
+  </si>
+  <si>
+    <t>Prchile-35124</t>
+  </si>
+  <si>
+    <t>Prchile-35125</t>
+  </si>
+  <si>
+    <t>Prchile-35126</t>
+  </si>
+  <si>
+    <t>Prchile-35127</t>
+  </si>
+  <si>
+    <t>Prchile-35128</t>
+  </si>
+  <si>
+    <t>Prchile-35129</t>
+  </si>
+  <si>
+    <t>Prchile-35130</t>
+  </si>
+  <si>
+    <t>Prchile-35131</t>
+  </si>
+  <si>
+    <t>Prchile-35132</t>
+  </si>
+  <si>
+    <t>Prchile-35133</t>
+  </si>
+  <si>
+    <t>Prchile-35134</t>
+  </si>
+  <si>
+    <t>Prchile-35135</t>
+  </si>
+  <si>
+    <t>Prchile-35136</t>
+  </si>
+  <si>
+    <t>Prchile-35137</t>
+  </si>
+  <si>
+    <t>Prchile-35138</t>
+  </si>
+  <si>
+    <t>Prchile-35139</t>
+  </si>
+  <si>
+    <t>Prchile-35140</t>
+  </si>
+  <si>
+    <t>Prchile-35141</t>
+  </si>
+  <si>
+    <t>Prchile-35142</t>
+  </si>
+  <si>
+    <t>Prchile-35143</t>
+  </si>
+  <si>
+    <t>Prchile-35144</t>
+  </si>
+  <si>
+    <t>Prchile-35145</t>
+  </si>
+  <si>
+    <t>Prchile-35146</t>
+  </si>
+  <si>
+    <t>Prchile-35147</t>
+  </si>
+  <si>
+    <t>Prchile-35148</t>
+  </si>
+  <si>
+    <t>Prchile-35149</t>
+  </si>
+  <si>
+    <t>Prchile-35150</t>
+  </si>
+  <si>
+    <t>Prchile-35151</t>
+  </si>
+  <si>
+    <t>Prchile-35152</t>
+  </si>
+  <si>
+    <t>Prchile-35153</t>
+  </si>
+  <si>
+    <t>Prchile-35154</t>
+  </si>
+  <si>
+    <t>Prchile-35155</t>
+  </si>
+  <si>
+    <t>Prchile-35156</t>
+  </si>
+  <si>
+    <t>Prchile-35157</t>
+  </si>
+  <si>
+    <t>Prchile-35158</t>
+  </si>
+  <si>
+    <t>Prchile-35159</t>
+  </si>
+  <si>
+    <t>Prchile-35160</t>
+  </si>
+  <si>
+    <t>Prchile-35161</t>
+  </si>
+  <si>
+    <t>Prchile-35162</t>
+  </si>
+  <si>
+    <t>Prchile-35163</t>
+  </si>
+  <si>
+    <t>Prchile-35164</t>
+  </si>
+  <si>
+    <t>Prchile-35165</t>
+  </si>
+  <si>
+    <t>Prchile-35166</t>
+  </si>
+  <si>
+    <t>Prchile-35167</t>
+  </si>
+  <si>
+    <t>Prchile-35168</t>
+  </si>
+  <si>
+    <t>Prchile-35169</t>
+  </si>
+  <si>
+    <t>Prchile-35170</t>
+  </si>
+  <si>
+    <t>Prchile-35171</t>
+  </si>
+  <si>
+    <t>Prchile-35172</t>
+  </si>
+  <si>
+    <t>Prchile-35173</t>
+  </si>
+  <si>
+    <t>Prchile-35174</t>
+  </si>
+  <si>
+    <t>Prchile-35175</t>
+  </si>
+  <si>
+    <t>Prchile-35176</t>
+  </si>
+  <si>
+    <t>Prchile-35177</t>
+  </si>
+  <si>
+    <t>Prchile-35178</t>
+  </si>
+  <si>
+    <t>Prchile-35179</t>
+  </si>
+  <si>
+    <t>Prchile-35180</t>
+  </si>
+  <si>
+    <t>Prchile-35181</t>
+  </si>
+  <si>
+    <t>Prchile-35182</t>
+  </si>
+  <si>
+    <t>Prchile-35183</t>
+  </si>
+  <si>
+    <t>Prchile-35184</t>
+  </si>
+  <si>
+    <t>Prchile-35185</t>
+  </si>
+  <si>
+    <t>Prchile-35186</t>
+  </si>
+  <si>
+    <t>Prchile-35187</t>
+  </si>
+  <si>
+    <t>Prchile-35188</t>
+  </si>
+  <si>
+    <t>Prchile-35189</t>
+  </si>
+  <si>
+    <t>Prchile-35190</t>
+  </si>
+  <si>
+    <t>Prchile-35191</t>
+  </si>
+  <si>
+    <t>Prchile-35192</t>
+  </si>
+  <si>
+    <t>Prchile-35193</t>
+  </si>
+  <si>
+    <t>Prchile-35194</t>
+  </si>
+  <si>
+    <t>Prchile-35195</t>
+  </si>
+  <si>
+    <t>Prchile-35196</t>
+  </si>
+  <si>
+    <t>Prchile-35197</t>
+  </si>
+  <si>
+    <t>Prchile-35198</t>
+  </si>
+  <si>
+    <t>Prchile-35199</t>
+  </si>
+  <si>
+    <t>Prchile-35200</t>
+  </si>
+  <si>
+    <t>Prchile-35201</t>
+  </si>
+  <si>
+    <t>Prchile-35202</t>
+  </si>
+  <si>
+    <t>Prchile-35203</t>
+  </si>
+  <si>
+    <t>Prchile-35204</t>
+  </si>
+  <si>
+    <t>Prchile-35205</t>
+  </si>
+  <si>
+    <t>Prchile-35206</t>
+  </si>
+  <si>
+    <t>Prchile-35207</t>
+  </si>
+  <si>
+    <t>Prchile-35208</t>
+  </si>
+  <si>
+    <t>Prchile-35209</t>
+  </si>
+  <si>
+    <t>Prchile-35210</t>
+  </si>
+  <si>
+    <t>Prchile-35211</t>
+  </si>
+  <si>
+    <t>Prchile-35212</t>
+  </si>
+  <si>
+    <t>Prchile-35213</t>
+  </si>
+  <si>
+    <t>Prchile-35214</t>
+  </si>
+  <si>
+    <t>Prchile-35215</t>
+  </si>
+  <si>
+    <t>Prchile-35216</t>
+  </si>
+  <si>
+    <t>Prchile-35217</t>
+  </si>
+  <si>
+    <t>Prchile-35218</t>
+  </si>
+  <si>
+    <t>Prchile-35219</t>
+  </si>
+  <si>
+    <t>Prchile-35220</t>
+  </si>
+  <si>
+    <t>Prchile-35221</t>
+  </si>
+  <si>
+    <t>Prchile-35222</t>
+  </si>
+  <si>
+    <t>Prchile-35223</t>
+  </si>
+  <si>
+    <t>Prchile-35224</t>
+  </si>
+  <si>
+    <t>Prchile-35225</t>
+  </si>
+  <si>
+    <t>Prchile-35226</t>
+  </si>
+  <si>
+    <t>Prchile-35227</t>
+  </si>
+  <si>
+    <t>Prchile-35228</t>
+  </si>
+  <si>
+    <t>Prchile-35229</t>
+  </si>
+  <si>
+    <t>Prchile-35230</t>
+  </si>
+  <si>
+    <t>Prchile-35231</t>
+  </si>
+  <si>
+    <t>Prchile-35232</t>
+  </si>
+  <si>
+    <t>Prchile-35233</t>
+  </si>
+  <si>
+    <t>Prchile-35234</t>
+  </si>
+  <si>
+    <t>Prchile-35235</t>
+  </si>
+  <si>
+    <t>Prchile-35236</t>
+  </si>
+  <si>
+    <t>Prchile-35237</t>
+  </si>
+  <si>
+    <t>Prchile-35238</t>
+  </si>
+  <si>
+    <t>Prchile-35239</t>
+  </si>
+  <si>
+    <t>Prchile-35240</t>
+  </si>
+  <si>
+    <t>Prchile-35241</t>
+  </si>
+  <si>
+    <t>Prchile-35242</t>
+  </si>
+  <si>
+    <t>Prchile-35243</t>
+  </si>
+  <si>
+    <t>Prchile-35244</t>
+  </si>
+  <si>
+    <t>Prchile-35245</t>
+  </si>
+  <si>
+    <t>Prchile-35246</t>
+  </si>
+  <si>
+    <t>Prchile-35247</t>
+  </si>
+  <si>
+    <t>Prchile-35248</t>
+  </si>
+  <si>
+    <t>Prchile-35249</t>
+  </si>
+  <si>
+    <t>Prchile-35250</t>
+  </si>
+  <si>
+    <t>Prchile-35251</t>
+  </si>
+  <si>
+    <t>Prchile-35252</t>
+  </si>
+  <si>
+    <t>Prchile-35253</t>
+  </si>
+  <si>
+    <t>Prchile-35254</t>
+  </si>
+  <si>
+    <t>Prchile-35255</t>
+  </si>
+  <si>
+    <t>Prchile-35256</t>
+  </si>
+  <si>
+    <t>Prchile-35257</t>
+  </si>
+  <si>
+    <t>Prchile-35258</t>
+  </si>
+  <si>
+    <t>Prchile-35259</t>
+  </si>
+  <si>
+    <t>Prchile-35260</t>
+  </si>
+  <si>
+    <t>Prchile-35261</t>
+  </si>
+  <si>
+    <t>Prchile-35262</t>
+  </si>
+  <si>
+    <t>Prchile-35263</t>
+  </si>
+  <si>
+    <t>Prchile-35264</t>
+  </si>
+  <si>
+    <t>Prchile-35265</t>
+  </si>
+  <si>
+    <t>Prchile-35266</t>
+  </si>
+  <si>
+    <t>Prchile-35267</t>
+  </si>
+  <si>
+    <t>Prchile-35268</t>
+  </si>
+  <si>
+    <t>Prchile-35269</t>
+  </si>
+  <si>
+    <t>Prchile-35270</t>
+  </si>
+  <si>
+    <t>Prchile-35271</t>
+  </si>
+  <si>
+    <t>Prchile-35272</t>
+  </si>
+  <si>
+    <t>Prchile-35273</t>
+  </si>
+  <si>
+    <t>Prchile-35274</t>
+  </si>
+  <si>
+    <t>Prchile-35275</t>
+  </si>
+  <si>
+    <t>Prchile-35276</t>
+  </si>
+  <si>
+    <t>Prchile-35277</t>
+  </si>
+  <si>
+    <t>Prchile-35278</t>
+  </si>
+  <si>
+    <t>Prchile-35279</t>
+  </si>
+  <si>
+    <t>Prchile-35280</t>
+  </si>
+  <si>
+    <t>Prchile-35281</t>
+  </si>
+  <si>
+    <t>Prchile-35282</t>
+  </si>
+  <si>
+    <t>Prchile-35283</t>
+  </si>
+  <si>
+    <t>Prchile-35284</t>
+  </si>
+  <si>
+    <t>Prchile-35285</t>
+  </si>
+  <si>
+    <t>Prchile-35286</t>
+  </si>
+  <si>
+    <t>Prchile-35287</t>
+  </si>
+  <si>
+    <t>Prchile-35288</t>
+  </si>
+  <si>
+    <t>Prchile-35289</t>
+  </si>
+  <si>
+    <t>Prchile-35290</t>
+  </si>
+  <si>
+    <t>Prchile-35291</t>
+  </si>
+  <si>
+    <t>Prchile-35292</t>
+  </si>
+  <si>
+    <t>Prchile-35293</t>
+  </si>
+  <si>
+    <t>Prchile-35294</t>
+  </si>
+  <si>
+    <t>Prchile-35295</t>
+  </si>
+  <si>
+    <t>Prchile-35296</t>
+  </si>
+  <si>
+    <t>Prchile-35297</t>
+  </si>
+  <si>
+    <t>Prchile-35298</t>
+  </si>
+  <si>
+    <t>Prchile-35299</t>
+  </si>
+  <si>
+    <t>Prchile-35300</t>
+  </si>
+  <si>
+    <t>Prchile-35301</t>
+  </si>
+  <si>
+    <t>Prchile-35302</t>
+  </si>
+  <si>
+    <t>Prchile-35303</t>
+  </si>
+  <si>
+    <t>Prchile-35304</t>
+  </si>
+  <si>
+    <t>Prchile-35305</t>
+  </si>
+  <si>
+    <t>Prchile-35306</t>
+  </si>
+  <si>
+    <t>Prchile-35307</t>
+  </si>
+  <si>
+    <t>Prchile-35308</t>
+  </si>
+  <si>
+    <t>Prchile-35309</t>
+  </si>
+  <si>
+    <t>Prchile-35310</t>
+  </si>
+  <si>
+    <t>Prchile-35311</t>
+  </si>
+  <si>
+    <t>Prchile-35312</t>
+  </si>
+  <si>
+    <t>Prchile-35313</t>
+  </si>
+  <si>
+    <t>Prchile-35314</t>
+  </si>
+  <si>
+    <t>Prchile-35315</t>
+  </si>
+  <si>
+    <t>Prchile-35316</t>
+  </si>
+  <si>
+    <t>Prchile-35317</t>
+  </si>
+  <si>
+    <t>Prchile-35318</t>
+  </si>
+  <si>
+    <t>Prchile-35319</t>
+  </si>
+  <si>
+    <t>Prchile-35320</t>
+  </si>
+  <si>
+    <t>Prchile-35321</t>
+  </si>
+  <si>
+    <t>Prchile-35322</t>
+  </si>
+  <si>
+    <t>Prchile-35323</t>
+  </si>
+  <si>
+    <t>Prchile-35324</t>
+  </si>
+  <si>
+    <t>Prchile-35325</t>
+  </si>
+  <si>
+    <t>Prchile-35326</t>
+  </si>
+  <si>
+    <t>Prchile-35327</t>
+  </si>
+  <si>
+    <t>Prchile-35328</t>
+  </si>
+  <si>
+    <t>Prchile-35329</t>
+  </si>
+  <si>
+    <t>Prchile-35330</t>
+  </si>
+  <si>
+    <t>Prchile-35331</t>
+  </si>
+  <si>
+    <t>Prchile-35332</t>
+  </si>
+  <si>
+    <t>Prchile-35333</t>
+  </si>
+  <si>
+    <t>Prchile-35334</t>
+  </si>
+  <si>
+    <t>Prchile-35335</t>
+  </si>
+  <si>
+    <t>Prchile-35336</t>
+  </si>
+  <si>
+    <t>Prchile-35337</t>
+  </si>
+  <si>
+    <t>Prchile-35338</t>
+  </si>
+  <si>
+    <t>Prchile-35339</t>
+  </si>
+  <si>
+    <t>Prchile-35340</t>
+  </si>
+  <si>
+    <t>Prchile-35341</t>
+  </si>
+  <si>
+    <t>Prchile-35342</t>
+  </si>
+  <si>
+    <t>Prchile-35343</t>
+  </si>
+  <si>
+    <t>Prchile-35344</t>
+  </si>
+  <si>
+    <t>Prchile-35345</t>
+  </si>
+  <si>
+    <t>Prchile-35346</t>
+  </si>
+  <si>
+    <t>Prchile-35347</t>
+  </si>
+  <si>
+    <t>Prchile-35348</t>
+  </si>
+  <si>
+    <t>Prchile-35349</t>
+  </si>
+  <si>
+    <t>Prchile-35350</t>
+  </si>
+  <si>
+    <t>Prchile-35351</t>
+  </si>
+  <si>
+    <t>Prchile-35352</t>
+  </si>
+  <si>
+    <t>Prchile-35353</t>
+  </si>
+  <si>
+    <t>Prchile-35354</t>
+  </si>
+  <si>
+    <t>Prchile-35355</t>
+  </si>
+  <si>
+    <t>Prchile-35356</t>
+  </si>
+  <si>
+    <t>Prchile-35357</t>
+  </si>
+  <si>
+    <t>Prchile-35358</t>
+  </si>
+  <si>
+    <t>Prchile-35359</t>
+  </si>
+  <si>
+    <t>Prchile-35360</t>
+  </si>
+  <si>
+    <t>Prchile-35361</t>
+  </si>
+  <si>
+    <t>Prchile-35362</t>
+  </si>
+  <si>
+    <t>Prchile-35363</t>
+  </si>
+  <si>
+    <t>Prchile-35364</t>
+  </si>
+  <si>
+    <t>Prchile-35365</t>
+  </si>
+  <si>
+    <t>Prchile-35366</t>
+  </si>
+  <si>
+    <t>Prchile-35367</t>
+  </si>
+  <si>
+    <t>Prchile-35368</t>
+  </si>
+  <si>
+    <t>Prchile-35369</t>
+  </si>
+  <si>
+    <t>Prchile-35370</t>
+  </si>
+  <si>
+    <t>Prchile-35371</t>
+  </si>
+  <si>
+    <t>Prchile-35372</t>
+  </si>
+  <si>
+    <t>Prchile-35373</t>
+  </si>
+  <si>
+    <t>Prchile-35374</t>
+  </si>
+  <si>
+    <t>Prchile-35375</t>
+  </si>
+  <si>
+    <t>Prchile-35376</t>
+  </si>
+  <si>
+    <t>Prchile-35377</t>
+  </si>
+  <si>
+    <t>Prchile-35378</t>
+  </si>
+  <si>
+    <t>Prchile-35379</t>
+  </si>
+  <si>
+    <t>Prchile-35380</t>
+  </si>
+  <si>
+    <t>Prchile-35381</t>
+  </si>
+  <si>
+    <t>Prchile-35382</t>
+  </si>
+  <si>
+    <t>Prchile-35383</t>
+  </si>
+  <si>
+    <t>Prchile-35384</t>
+  </si>
+  <si>
+    <t>Prchile-35385</t>
+  </si>
+  <si>
+    <t>Prchile-35386</t>
+  </si>
+  <si>
+    <t>Prchile-35387</t>
+  </si>
+  <si>
+    <t>Prchile-35388</t>
+  </si>
+  <si>
+    <t>Prchile-35389</t>
+  </si>
+  <si>
+    <t>Prchile-35390</t>
+  </si>
+  <si>
+    <t>Prchile-35391</t>
+  </si>
+  <si>
+    <t>Prchile-35392</t>
+  </si>
+  <si>
+    <t>Prchile-35393</t>
+  </si>
+  <si>
+    <t>Prchile-35394</t>
+  </si>
+  <si>
+    <t>Prchile-35395</t>
+  </si>
+  <si>
+    <t>Prchile-35396</t>
+  </si>
+  <si>
+    <t>Prchile-35397</t>
+  </si>
+  <si>
+    <t>Prchile-35398</t>
+  </si>
+  <si>
+    <t>Prchile-35399</t>
+  </si>
+  <si>
+    <t>Prchile-35400</t>
+  </si>
+  <si>
+    <t>Prchile-35401</t>
+  </si>
+  <si>
+    <t>Prchile-35402</t>
+  </si>
+  <si>
+    <t>Prchile-35403</t>
+  </si>
+  <si>
+    <t>Prchile-35404</t>
+  </si>
+  <si>
+    <t>Prchile-35405</t>
+  </si>
+  <si>
+    <t>Prchile-35406</t>
+  </si>
+  <si>
+    <t>Prchile-35407</t>
+  </si>
+  <si>
+    <t>Prchile-35408</t>
+  </si>
+  <si>
+    <t>Prchile-35409</t>
+  </si>
+  <si>
+    <t>Prchile-35410</t>
+  </si>
+  <si>
+    <t>Prchile-35411</t>
+  </si>
+  <si>
+    <t>Prchile-35412</t>
+  </si>
+  <si>
+    <t>Prchile-35413</t>
+  </si>
+  <si>
+    <t>Prchile-35414</t>
+  </si>
+  <si>
+    <t>Prchile-35415</t>
+  </si>
+  <si>
+    <t>Prchile-35416</t>
+  </si>
+  <si>
+    <t>Prchile-35417</t>
+  </si>
+  <si>
+    <t>Prchile-35418</t>
+  </si>
+  <si>
+    <t>Prchile-35419</t>
+  </si>
+  <si>
+    <t>Prchile-35420</t>
+  </si>
+  <si>
+    <t>Prchile-35421</t>
+  </si>
+  <si>
+    <t>Prchile-35422</t>
+  </si>
+  <si>
+    <t>Prchile-35423</t>
+  </si>
+  <si>
+    <t>Prchile-35424</t>
+  </si>
+  <si>
+    <t>Prchile-35425</t>
+  </si>
+  <si>
+    <t>Prchile-35426</t>
+  </si>
+  <si>
+    <t>Prchile-35427</t>
+  </si>
+  <si>
+    <t>Prchile-35428</t>
+  </si>
+  <si>
+    <t>Prchile-35429</t>
+  </si>
+  <si>
+    <t>Prchile-35430</t>
+  </si>
+  <si>
+    <t>Prchile-35431</t>
+  </si>
+  <si>
+    <t>Prchile-35432</t>
+  </si>
+  <si>
+    <t>Prchile-35433</t>
+  </si>
+  <si>
+    <t>Prchile-35434</t>
+  </si>
+  <si>
+    <t>Prchile-35435</t>
+  </si>
+  <si>
+    <t>Prchile-35436</t>
+  </si>
+  <si>
+    <t>Prchile-35437</t>
+  </si>
+  <si>
+    <t>Prchile-35438</t>
+  </si>
+  <si>
+    <t>Prchile-35439</t>
+  </si>
+  <si>
+    <t>Prchile-35440</t>
+  </si>
+  <si>
+    <t>Prchile-35441</t>
+  </si>
+  <si>
+    <t>Prchile-35442</t>
+  </si>
+  <si>
+    <t>Prchile-35443</t>
+  </si>
+  <si>
+    <t>Prchile-35444</t>
+  </si>
+  <si>
+    <t>Prchile-35445</t>
+  </si>
+  <si>
+    <t>Prchile-35446</t>
+  </si>
+  <si>
+    <t>Prchile-35447</t>
+  </si>
+  <si>
+    <t>Prchile-35448</t>
+  </si>
+  <si>
+    <t>Prchile-35449</t>
+  </si>
+  <si>
+    <t>Prchile-35450</t>
+  </si>
+  <si>
+    <t>Prchile-35451</t>
+  </si>
+  <si>
+    <t>Prchile-35452</t>
+  </si>
+  <si>
+    <t>Prchile-35453</t>
+  </si>
+  <si>
+    <t>Prchile-35454</t>
+  </si>
+  <si>
+    <t>Prchile-35455</t>
+  </si>
+  <si>
+    <t>Prchile-35456</t>
+  </si>
+  <si>
+    <t>Prchile-35457</t>
+  </si>
+  <si>
+    <t>Prchile-35458</t>
+  </si>
+  <si>
+    <t>Prchile-35459</t>
+  </si>
+  <si>
+    <t>Prchile-35460</t>
+  </si>
+  <si>
+    <t>Prchile-35461</t>
+  </si>
+  <si>
+    <t>Prchile-35462</t>
+  </si>
+  <si>
+    <t>Prchile-35463</t>
+  </si>
+  <si>
+    <t>Prchile-35464</t>
+  </si>
+  <si>
+    <t>Prchile-35465</t>
+  </si>
+  <si>
+    <t>Prchile-35466</t>
+  </si>
+  <si>
+    <t>Prchile-35467</t>
+  </si>
+  <si>
+    <t>Prchile-35468</t>
+  </si>
+  <si>
+    <t>Prchile-35469</t>
+  </si>
+  <si>
+    <t>Prchile-35470</t>
+  </si>
+  <si>
+    <t>Prchile-35471</t>
+  </si>
+  <si>
+    <t>Prchile-35472</t>
+  </si>
+  <si>
+    <t>Prchile-35473</t>
+  </si>
+  <si>
+    <t>Prchile-35474</t>
+  </si>
+  <si>
+    <t>Prchile-35475</t>
+  </si>
+  <si>
+    <t>Prchile-35476</t>
+  </si>
+  <si>
+    <t>Prchile-35477</t>
+  </si>
+  <si>
+    <t>Prchile-35478</t>
+  </si>
+  <si>
+    <t>Prchile-35479</t>
+  </si>
+  <si>
+    <t>Prchile-35480</t>
+  </si>
+  <si>
+    <t>Prchile-35481</t>
+  </si>
+  <si>
+    <t>Prchile-35482</t>
+  </si>
+  <si>
+    <t>Prchile-35483</t>
+  </si>
+  <si>
+    <t>Prchile-35484</t>
+  </si>
+  <si>
+    <t>Prchile-35485</t>
+  </si>
+  <si>
+    <t>Prchile-35486</t>
+  </si>
+  <si>
+    <t>Prchile-35487</t>
+  </si>
+  <si>
+    <t>Prchile-35488</t>
+  </si>
+  <si>
+    <t>Prchile-35489</t>
+  </si>
+  <si>
+    <t>Prchile-35490</t>
+  </si>
+  <si>
+    <t>Prchile-35491</t>
+  </si>
+  <si>
+    <t>Prchile-35492</t>
+  </si>
+  <si>
+    <t>Prchile-35493</t>
+  </si>
+  <si>
+    <t>Prchile-35494</t>
+  </si>
+  <si>
+    <t>Prchile-35495</t>
+  </si>
+  <si>
+    <t>Prchile-35496</t>
+  </si>
+  <si>
+    <t>Prchile-35497</t>
+  </si>
+  <si>
+    <t>Prchile-35498</t>
+  </si>
+  <si>
+    <t>Prchile-35499</t>
+  </si>
+  <si>
+    <t>Prchile-35500</t>
+  </si>
+  <si>
+    <t>Prchile-35501</t>
+  </si>
+  <si>
+    <t>Prchile-35502</t>
+  </si>
+  <si>
+    <t>Prchile-35503</t>
+  </si>
+  <si>
+    <t>Prchile-35504</t>
+  </si>
+  <si>
+    <t>Prchile-35505</t>
+  </si>
+  <si>
+    <t>Prchile-35506</t>
+  </si>
+  <si>
+    <t>Prchile-35507</t>
+  </si>
+  <si>
+    <t>Prchile-35508</t>
+  </si>
+  <si>
+    <t>Prchile-35509</t>
+  </si>
+  <si>
+    <t>Prchile-35510</t>
+  </si>
+  <si>
+    <t>Prchile-35511</t>
+  </si>
+  <si>
+    <t>Prchile-35512</t>
+  </si>
+  <si>
+    <t>Prchile-35513</t>
+  </si>
+  <si>
+    <t>Prchile-35514</t>
+  </si>
+  <si>
+    <t>Prchile-35515</t>
+  </si>
+  <si>
+    <t>Prchile-35516</t>
+  </si>
+  <si>
+    <t>Prchile-35517</t>
+  </si>
+  <si>
+    <t>Prchile-35518</t>
+  </si>
+  <si>
+    <t>Prchile-35519</t>
+  </si>
+  <si>
+    <t>Prchile-35520</t>
+  </si>
+  <si>
+    <t>Prchile-35521</t>
+  </si>
+  <si>
+    <t>Prchile-35522</t>
+  </si>
+  <si>
+    <t>Prchile-35523</t>
+  </si>
+  <si>
+    <t>Prchile-35524</t>
+  </si>
+  <si>
+    <t>Prchile-35525</t>
+  </si>
+  <si>
+    <t>Prchile-35526</t>
+  </si>
+  <si>
+    <t>Prchile-35527</t>
+  </si>
+  <si>
+    <t>Prchile-35528</t>
+  </si>
+  <si>
+    <t>Prchile-35529</t>
+  </si>
+  <si>
+    <t>Prchile-35530</t>
+  </si>
+  <si>
+    <t>Prchile-35531</t>
+  </si>
+  <si>
+    <t>Prchile-35532</t>
+  </si>
+  <si>
+    <t>Prchile-35533</t>
+  </si>
+  <si>
+    <t>Prchile-35534</t>
+  </si>
+  <si>
+    <t>Prchile-35535</t>
+  </si>
+  <si>
+    <t>Prchile-35536</t>
+  </si>
+  <si>
+    <t>Prchile-35537</t>
+  </si>
+  <si>
+    <t>Prchile-35538</t>
+  </si>
+  <si>
+    <t>Prchile-35539</t>
+  </si>
+  <si>
+    <t>Prchile-35540</t>
+  </si>
+  <si>
+    <t>Prchile-35541</t>
+  </si>
+  <si>
+    <t>Prchile-35542</t>
+  </si>
+  <si>
+    <t>Prchile-35543</t>
+  </si>
+  <si>
+    <t>Prchile-35544</t>
+  </si>
+  <si>
+    <t>Prchile-35545</t>
+  </si>
+  <si>
+    <t>Prchile-35546</t>
+  </si>
+  <si>
+    <t>Prchile-35547</t>
+  </si>
+  <si>
+    <t>Prchile-35548</t>
+  </si>
+  <si>
+    <t>Prchile-35549</t>
+  </si>
+  <si>
+    <t>Prchile-35550</t>
+  </si>
+  <si>
+    <t>Prchile-35551</t>
+  </si>
+  <si>
+    <t>Prchile-35552</t>
+  </si>
+  <si>
+    <t>Prchile-35553</t>
+  </si>
+  <si>
+    <t>Prchile-35554</t>
+  </si>
+  <si>
+    <t>Prchile-35555</t>
+  </si>
+  <si>
+    <t>Prchile-35556</t>
+  </si>
+  <si>
+    <t>Prchile-35557</t>
+  </si>
+  <si>
+    <t>Prchile-35558</t>
+  </si>
+  <si>
+    <t>Prchile-35559</t>
+  </si>
+  <si>
+    <t>Prchile-35560</t>
+  </si>
+  <si>
+    <t>Prchile-35561</t>
+  </si>
+  <si>
+    <t>Prchile-35562</t>
+  </si>
+  <si>
+    <t>Prchile-35563</t>
+  </si>
+  <si>
+    <t>Prchile-35564</t>
+  </si>
+  <si>
+    <t>Prchile-35565</t>
+  </si>
+  <si>
+    <t>Prchile-35566</t>
+  </si>
+  <si>
+    <t>Prchile-35567</t>
+  </si>
+  <si>
+    <t>Prchile-35568</t>
+  </si>
+  <si>
+    <t>Prchile-35569</t>
+  </si>
+  <si>
+    <t>Prchile-35570</t>
+  </si>
+  <si>
+    <t>Prchile-35571</t>
+  </si>
+  <si>
+    <t>Prchile-35572</t>
+  </si>
+  <si>
+    <t>Prchile-35573</t>
+  </si>
+  <si>
+    <t>Prchile-35574</t>
+  </si>
+  <si>
+    <t>Prchile-35575</t>
+  </si>
+  <si>
+    <t>Prchile-35576</t>
+  </si>
+  <si>
+    <t>Prchile-35577</t>
+  </si>
+  <si>
+    <t>Prchile-35578</t>
+  </si>
+  <si>
+    <t>Prchile-35579</t>
+  </si>
+  <si>
+    <t>Prchile-35580</t>
+  </si>
+  <si>
+    <t>Prchile-35581</t>
+  </si>
+  <si>
+    <t>Prchile-35582</t>
+  </si>
+  <si>
+    <t>Prchile-35583</t>
+  </si>
+  <si>
+    <t>Prchile-35584</t>
+  </si>
+  <si>
+    <t>Prchile-35585</t>
+  </si>
+  <si>
+    <t>Prchile-35586</t>
+  </si>
+  <si>
+    <t>Prchile-35587</t>
+  </si>
+  <si>
+    <t>Prchile-35588</t>
+  </si>
+  <si>
+    <t>Prchile-35589</t>
+  </si>
+  <si>
+    <t>Prchile-35590</t>
+  </si>
+  <si>
+    <t>Prchile-35591</t>
+  </si>
+  <si>
+    <t>Prchile-35592</t>
+  </si>
+  <si>
+    <t>Prchile-35593</t>
+  </si>
+  <si>
+    <t>Prchile-35594</t>
+  </si>
+  <si>
+    <t>Prchile-35595</t>
+  </si>
+  <si>
+    <t>Prchile-35596</t>
+  </si>
+  <si>
+    <t>Prchile-35597</t>
+  </si>
+  <si>
+    <t>Prchile-35598</t>
+  </si>
+  <si>
+    <t>Prchile-35599</t>
+  </si>
+  <si>
+    <t>Prchile-35600</t>
+  </si>
+  <si>
+    <t>Prchile-35601</t>
+  </si>
+  <si>
+    <t>Prchile-35602</t>
+  </si>
+  <si>
+    <t>Prchile-35603</t>
+  </si>
+  <si>
+    <t>Prchile-35604</t>
+  </si>
+  <si>
+    <t>Prchile-35605</t>
+  </si>
+  <si>
+    <t>Prchile-35606</t>
+  </si>
+  <si>
+    <t>Prchile-35607</t>
+  </si>
+  <si>
+    <t>Prchile-35608</t>
+  </si>
+  <si>
+    <t>Prchile-35609</t>
+  </si>
+  <si>
+    <t>Prchile-35610</t>
+  </si>
+  <si>
+    <t>Prchile-35611</t>
+  </si>
+  <si>
+    <t>Prchile-35612</t>
+  </si>
+  <si>
+    <t>Prchile-35613</t>
+  </si>
+  <si>
+    <t>Prchile-35614</t>
+  </si>
+  <si>
+    <t>Prchile-35615</t>
+  </si>
+  <si>
+    <t>Prchile-35616</t>
+  </si>
+  <si>
+    <t>Prchile-35617</t>
+  </si>
+  <si>
+    <t>Prchile-35618</t>
+  </si>
+  <si>
+    <t>Prchile-35619</t>
+  </si>
+  <si>
+    <t>Prchile-35620</t>
+  </si>
+  <si>
+    <t>Prchile-35621</t>
+  </si>
+  <si>
+    <t>Prchile-35622</t>
+  </si>
+  <si>
+    <t>Prchile-35623</t>
+  </si>
+  <si>
+    <t>Prchile-35624</t>
+  </si>
+  <si>
+    <t>Prchile-35625</t>
+  </si>
+  <si>
+    <t>Prchile-35626</t>
+  </si>
+  <si>
+    <t>Prchile-35627</t>
+  </si>
+  <si>
+    <t>Prchile-35628</t>
+  </si>
+  <si>
+    <t>Prchile-35629</t>
+  </si>
+  <si>
+    <t>Prchile-35630</t>
+  </si>
+  <si>
+    <t>Prchile-35631</t>
+  </si>
+  <si>
+    <t>Prchile-35632</t>
+  </si>
+  <si>
+    <t>Prchile-35633</t>
+  </si>
+  <si>
+    <t>Prchile-35634</t>
+  </si>
+  <si>
+    <t>Prchile-35635</t>
+  </si>
+  <si>
+    <t>Prchile-35636</t>
+  </si>
+  <si>
+    <t>Prchile-35637</t>
+  </si>
+  <si>
+    <t>Prchile-35638</t>
+  </si>
+  <si>
+    <t>Prchile-35639</t>
+  </si>
+  <si>
+    <t>Prchile-35640</t>
+  </si>
+  <si>
+    <t>Prchile-35641</t>
+  </si>
+  <si>
+    <t>Prchile-35642</t>
+  </si>
+  <si>
+    <t>Prchile-35643</t>
+  </si>
+  <si>
+    <t>Prchile-35644</t>
+  </si>
+  <si>
+    <t>Prchile-35645</t>
+  </si>
+  <si>
+    <t>Prchile-35646</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +3416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1774,6 +3424,10 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
@@ -2122,7 +3776,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>557</v>
       </c>
       <c r="C1" t="s">
@@ -2157,9 +3811,8 @@
       <c r="A2" s="2">
         <v>35097</v>
       </c>
-      <c r="B2" t="str">
-        <f>$B$1&amp;"-"&amp;A2</f>
-        <v>Prchile-35097</v>
+      <c r="B2" s="4" t="s">
+        <v>558</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -2193,9 +3846,8 @@
       <c r="A3" s="2">
         <v>35098</v>
       </c>
-      <c r="B3" t="str">
-        <f t="shared" ref="B3:B66" si="0">$B$1&amp;"-"&amp;A3</f>
-        <v>Prchile-35098</v>
+      <c r="B3" t="s">
+        <v>559</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -2229,9 +3881,8 @@
       <c r="A4" s="2">
         <v>35099</v>
       </c>
-      <c r="B4" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35099</v>
+      <c r="B4" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -2265,9 +3916,8 @@
       <c r="A5" s="2">
         <v>35100</v>
       </c>
-      <c r="B5" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35100</v>
+      <c r="B5" t="s">
+        <v>561</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -2301,9 +3951,8 @@
       <c r="A6" s="2">
         <v>35101</v>
       </c>
-      <c r="B6" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35101</v>
+      <c r="B6" s="4" t="s">
+        <v>562</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -2337,9 +3986,8 @@
       <c r="A7" s="2">
         <v>35102</v>
       </c>
-      <c r="B7" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35102</v>
+      <c r="B7" t="s">
+        <v>563</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -2373,9 +4021,8 @@
       <c r="A8" s="2">
         <v>35103</v>
       </c>
-      <c r="B8" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35103</v>
+      <c r="B8" s="4" t="s">
+        <v>564</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
@@ -2409,9 +4056,8 @@
       <c r="A9" s="2">
         <v>35104</v>
       </c>
-      <c r="B9" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35104</v>
+      <c r="B9" t="s">
+        <v>565</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -2445,9 +4091,8 @@
       <c r="A10" s="2">
         <v>35105</v>
       </c>
-      <c r="B10" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35105</v>
+      <c r="B10" s="4" t="s">
+        <v>566</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
@@ -2481,9 +4126,8 @@
       <c r="A11" s="2">
         <v>35106</v>
       </c>
-      <c r="B11" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35106</v>
+      <c r="B11" t="s">
+        <v>567</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -2517,9 +4161,8 @@
       <c r="A12" s="2">
         <v>35107</v>
       </c>
-      <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35107</v>
+      <c r="B12" s="4" t="s">
+        <v>568</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -2553,9 +4196,8 @@
       <c r="A13" s="2">
         <v>35108</v>
       </c>
-      <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35108</v>
+      <c r="B13" t="s">
+        <v>569</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -2589,9 +4231,8 @@
       <c r="A14" s="2">
         <v>35109</v>
       </c>
-      <c r="B14" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35109</v>
+      <c r="B14" s="4" t="s">
+        <v>570</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
@@ -2625,9 +4266,8 @@
       <c r="A15" s="2">
         <v>35110</v>
       </c>
-      <c r="B15" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35110</v>
+      <c r="B15" t="s">
+        <v>571</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
@@ -2661,9 +4301,8 @@
       <c r="A16" s="2">
         <v>35111</v>
       </c>
-      <c r="B16" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35111</v>
+      <c r="B16" s="4" t="s">
+        <v>572</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
@@ -2697,9 +4336,8 @@
       <c r="A17" s="2">
         <v>35112</v>
       </c>
-      <c r="B17" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35112</v>
+      <c r="B17" t="s">
+        <v>573</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -2733,9 +4371,8 @@
       <c r="A18" s="2">
         <v>35113</v>
       </c>
-      <c r="B18" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35113</v>
+      <c r="B18" s="4" t="s">
+        <v>574</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -2769,9 +4406,8 @@
       <c r="A19" s="2">
         <v>35114</v>
       </c>
-      <c r="B19" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35114</v>
+      <c r="B19" t="s">
+        <v>575</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -2805,9 +4441,8 @@
       <c r="A20" s="2">
         <v>35115</v>
       </c>
-      <c r="B20" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35115</v>
+      <c r="B20" s="4" t="s">
+        <v>576</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
@@ -2841,9 +4476,8 @@
       <c r="A21" s="2">
         <v>35116</v>
       </c>
-      <c r="B21" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35116</v>
+      <c r="B21" t="s">
+        <v>577</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
@@ -2877,9 +4511,8 @@
       <c r="A22" s="2">
         <v>35117</v>
       </c>
-      <c r="B22" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35117</v>
+      <c r="B22" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
@@ -2913,9 +4546,8 @@
       <c r="A23" s="2">
         <v>35118</v>
       </c>
-      <c r="B23" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35118</v>
+      <c r="B23" t="s">
+        <v>579</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -2949,9 +4581,8 @@
       <c r="A24" s="2">
         <v>35119</v>
       </c>
-      <c r="B24" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35119</v>
+      <c r="B24" s="4" t="s">
+        <v>580</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
@@ -2985,9 +4616,8 @@
       <c r="A25" s="2">
         <v>35120</v>
       </c>
-      <c r="B25" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35120</v>
+      <c r="B25" t="s">
+        <v>581</v>
       </c>
       <c r="C25" t="s">
         <v>39</v>
@@ -3021,9 +4651,8 @@
       <c r="A26" s="2">
         <v>35121</v>
       </c>
-      <c r="B26" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35121</v>
+      <c r="B26" s="4" t="s">
+        <v>582</v>
       </c>
       <c r="C26" t="s">
         <v>40</v>
@@ -3057,9 +4686,8 @@
       <c r="A27" s="2">
         <v>35122</v>
       </c>
-      <c r="B27" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35122</v>
+      <c r="B27" t="s">
+        <v>583</v>
       </c>
       <c r="C27" t="s">
         <v>41</v>
@@ -3093,9 +4721,8 @@
       <c r="A28" s="2">
         <v>35123</v>
       </c>
-      <c r="B28" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35123</v>
+      <c r="B28" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="C28" t="s">
         <v>42</v>
@@ -3129,9 +4756,8 @@
       <c r="A29" s="2">
         <v>35124</v>
       </c>
-      <c r="B29" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35124</v>
+      <c r="B29" t="s">
+        <v>585</v>
       </c>
       <c r="C29" t="s">
         <v>43</v>
@@ -3165,9 +4791,8 @@
       <c r="A30" s="2">
         <v>35125</v>
       </c>
-      <c r="B30" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35125</v>
+      <c r="B30" s="4" t="s">
+        <v>586</v>
       </c>
       <c r="C30" t="s">
         <v>44</v>
@@ -3201,9 +4826,8 @@
       <c r="A31" s="2">
         <v>35126</v>
       </c>
-      <c r="B31" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35126</v>
+      <c r="B31" t="s">
+        <v>587</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
@@ -3237,9 +4861,8 @@
       <c r="A32" s="2">
         <v>35127</v>
       </c>
-      <c r="B32" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35127</v>
+      <c r="B32" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="C32" t="s">
         <v>46</v>
@@ -3273,9 +4896,8 @@
       <c r="A33" s="2">
         <v>35128</v>
       </c>
-      <c r="B33" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35128</v>
+      <c r="B33" t="s">
+        <v>589</v>
       </c>
       <c r="C33" t="s">
         <v>47</v>
@@ -3309,9 +4931,8 @@
       <c r="A34" s="2">
         <v>35129</v>
       </c>
-      <c r="B34" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35129</v>
+      <c r="B34" s="4" t="s">
+        <v>590</v>
       </c>
       <c r="C34" t="s">
         <v>48</v>
@@ -3345,9 +4966,8 @@
       <c r="A35" s="2">
         <v>35130</v>
       </c>
-      <c r="B35" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35130</v>
+      <c r="B35" t="s">
+        <v>591</v>
       </c>
       <c r="C35" t="s">
         <v>49</v>
@@ -3381,9 +5001,8 @@
       <c r="A36" s="2">
         <v>35131</v>
       </c>
-      <c r="B36" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35131</v>
+      <c r="B36" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="C36" t="s">
         <v>50</v>
@@ -3417,9 +5036,8 @@
       <c r="A37" s="2">
         <v>35132</v>
       </c>
-      <c r="B37" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35132</v>
+      <c r="B37" t="s">
+        <v>593</v>
       </c>
       <c r="C37" t="s">
         <v>51</v>
@@ -3453,9 +5071,8 @@
       <c r="A38" s="2">
         <v>35133</v>
       </c>
-      <c r="B38" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35133</v>
+      <c r="B38" s="4" t="s">
+        <v>594</v>
       </c>
       <c r="C38" t="s">
         <v>52</v>
@@ -3489,9 +5106,8 @@
       <c r="A39" s="2">
         <v>35134</v>
       </c>
-      <c r="B39" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35134</v>
+      <c r="B39" t="s">
+        <v>595</v>
       </c>
       <c r="C39" t="s">
         <v>53</v>
@@ -3525,9 +5141,8 @@
       <c r="A40" s="2">
         <v>35135</v>
       </c>
-      <c r="B40" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35135</v>
+      <c r="B40" s="4" t="s">
+        <v>596</v>
       </c>
       <c r="C40" t="s">
         <v>54</v>
@@ -3561,9 +5176,8 @@
       <c r="A41" s="2">
         <v>35136</v>
       </c>
-      <c r="B41" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35136</v>
+      <c r="B41" t="s">
+        <v>597</v>
       </c>
       <c r="C41" t="s">
         <v>55</v>
@@ -3597,9 +5211,8 @@
       <c r="A42" s="2">
         <v>35137</v>
       </c>
-      <c r="B42" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35137</v>
+      <c r="B42" s="4" t="s">
+        <v>598</v>
       </c>
       <c r="C42" t="s">
         <v>56</v>
@@ -3633,9 +5246,8 @@
       <c r="A43" s="2">
         <v>35138</v>
       </c>
-      <c r="B43" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35138</v>
+      <c r="B43" t="s">
+        <v>599</v>
       </c>
       <c r="C43" t="s">
         <v>57</v>
@@ -3669,9 +5281,8 @@
       <c r="A44" s="2">
         <v>35139</v>
       </c>
-      <c r="B44" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35139</v>
+      <c r="B44" s="4" t="s">
+        <v>600</v>
       </c>
       <c r="C44" t="s">
         <v>58</v>
@@ -3705,9 +5316,8 @@
       <c r="A45" s="2">
         <v>35140</v>
       </c>
-      <c r="B45" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35140</v>
+      <c r="B45" t="s">
+        <v>601</v>
       </c>
       <c r="C45" t="s">
         <v>59</v>
@@ -3741,9 +5351,8 @@
       <c r="A46" s="2">
         <v>35141</v>
       </c>
-      <c r="B46" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35141</v>
+      <c r="B46" s="4" t="s">
+        <v>602</v>
       </c>
       <c r="C46" t="s">
         <v>60</v>
@@ -3777,9 +5386,8 @@
       <c r="A47" s="2">
         <v>35142</v>
       </c>
-      <c r="B47" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35142</v>
+      <c r="B47" t="s">
+        <v>603</v>
       </c>
       <c r="C47" t="s">
         <v>61</v>
@@ -3813,9 +5421,8 @@
       <c r="A48" s="2">
         <v>35143</v>
       </c>
-      <c r="B48" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35143</v>
+      <c r="B48" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="C48" t="s">
         <v>62</v>
@@ -3849,9 +5456,8 @@
       <c r="A49" s="2">
         <v>35144</v>
       </c>
-      <c r="B49" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35144</v>
+      <c r="B49" t="s">
+        <v>605</v>
       </c>
       <c r="C49" t="s">
         <v>63</v>
@@ -3885,9 +5491,8 @@
       <c r="A50" s="2">
         <v>35145</v>
       </c>
-      <c r="B50" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35145</v>
+      <c r="B50" s="4" t="s">
+        <v>606</v>
       </c>
       <c r="C50" t="s">
         <v>64</v>
@@ -3921,9 +5526,8 @@
       <c r="A51" s="2">
         <v>35146</v>
       </c>
-      <c r="B51" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35146</v>
+      <c r="B51" t="s">
+        <v>607</v>
       </c>
       <c r="C51" t="s">
         <v>65</v>
@@ -3957,9 +5561,8 @@
       <c r="A52" s="2">
         <v>35147</v>
       </c>
-      <c r="B52" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35147</v>
+      <c r="B52" s="4" t="s">
+        <v>608</v>
       </c>
       <c r="C52" t="s">
         <v>66</v>
@@ -3993,9 +5596,8 @@
       <c r="A53" s="2">
         <v>35148</v>
       </c>
-      <c r="B53" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35148</v>
+      <c r="B53" t="s">
+        <v>609</v>
       </c>
       <c r="C53" t="s">
         <v>67</v>
@@ -4029,9 +5631,8 @@
       <c r="A54" s="2">
         <v>35149</v>
       </c>
-      <c r="B54" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35149</v>
+      <c r="B54" s="4" t="s">
+        <v>610</v>
       </c>
       <c r="C54" t="s">
         <v>68</v>
@@ -4065,9 +5666,8 @@
       <c r="A55" s="2">
         <v>35150</v>
       </c>
-      <c r="B55" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35150</v>
+      <c r="B55" t="s">
+        <v>611</v>
       </c>
       <c r="C55" t="s">
         <v>69</v>
@@ -4101,9 +5701,8 @@
       <c r="A56" s="2">
         <v>35151</v>
       </c>
-      <c r="B56" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35151</v>
+      <c r="B56" s="4" t="s">
+        <v>612</v>
       </c>
       <c r="C56" t="s">
         <v>70</v>
@@ -4137,9 +5736,8 @@
       <c r="A57" s="2">
         <v>35152</v>
       </c>
-      <c r="B57" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35152</v>
+      <c r="B57" t="s">
+        <v>613</v>
       </c>
       <c r="C57" t="s">
         <v>71</v>
@@ -4173,9 +5771,8 @@
       <c r="A58" s="2">
         <v>35153</v>
       </c>
-      <c r="B58" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35153</v>
+      <c r="B58" s="4" t="s">
+        <v>614</v>
       </c>
       <c r="C58" t="s">
         <v>72</v>
@@ -4209,9 +5806,8 @@
       <c r="A59" s="2">
         <v>35154</v>
       </c>
-      <c r="B59" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35154</v>
+      <c r="B59" t="s">
+        <v>615</v>
       </c>
       <c r="C59" t="s">
         <v>73</v>
@@ -4245,9 +5841,8 @@
       <c r="A60" s="2">
         <v>35155</v>
       </c>
-      <c r="B60" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35155</v>
+      <c r="B60" s="4" t="s">
+        <v>616</v>
       </c>
       <c r="C60" t="s">
         <v>74</v>
@@ -4281,9 +5876,8 @@
       <c r="A61" s="2">
         <v>35156</v>
       </c>
-      <c r="B61" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35156</v>
+      <c r="B61" t="s">
+        <v>617</v>
       </c>
       <c r="C61" t="s">
         <v>75</v>
@@ -4317,9 +5911,8 @@
       <c r="A62" s="2">
         <v>35157</v>
       </c>
-      <c r="B62" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35157</v>
+      <c r="B62" s="4" t="s">
+        <v>618</v>
       </c>
       <c r="C62" t="s">
         <v>76</v>
@@ -4353,9 +5946,8 @@
       <c r="A63" s="2">
         <v>35158</v>
       </c>
-      <c r="B63" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35158</v>
+      <c r="B63" t="s">
+        <v>619</v>
       </c>
       <c r="C63" t="s">
         <v>77</v>
@@ -4389,9 +5981,8 @@
       <c r="A64" s="2">
         <v>35159</v>
       </c>
-      <c r="B64" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35159</v>
+      <c r="B64" s="4" t="s">
+        <v>620</v>
       </c>
       <c r="C64" t="s">
         <v>78</v>
@@ -4425,9 +6016,8 @@
       <c r="A65" s="2">
         <v>35160</v>
       </c>
-      <c r="B65" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35160</v>
+      <c r="B65" t="s">
+        <v>621</v>
       </c>
       <c r="C65" t="s">
         <v>79</v>
@@ -4461,9 +6051,8 @@
       <c r="A66" s="2">
         <v>35161</v>
       </c>
-      <c r="B66" t="str">
-        <f t="shared" si="0"/>
-        <v>Prchile-35161</v>
+      <c r="B66" s="4" t="s">
+        <v>622</v>
       </c>
       <c r="C66" t="s">
         <v>80</v>
@@ -4497,9 +6086,8 @@
       <c r="A67" s="2">
         <v>35162</v>
       </c>
-      <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="1">$B$1&amp;"-"&amp;A67</f>
-        <v>Prchile-35162</v>
+      <c r="B67" t="s">
+        <v>623</v>
       </c>
       <c r="C67" t="s">
         <v>81</v>
@@ -4533,9 +6121,8 @@
       <c r="A68" s="2">
         <v>35163</v>
       </c>
-      <c r="B68" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35163</v>
+      <c r="B68" s="4" t="s">
+        <v>624</v>
       </c>
       <c r="C68" t="s">
         <v>82</v>
@@ -4569,9 +6156,8 @@
       <c r="A69" s="2">
         <v>35164</v>
       </c>
-      <c r="B69" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35164</v>
+      <c r="B69" t="s">
+        <v>625</v>
       </c>
       <c r="C69" t="s">
         <v>83</v>
@@ -4605,9 +6191,8 @@
       <c r="A70" s="2">
         <v>35165</v>
       </c>
-      <c r="B70" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35165</v>
+      <c r="B70" s="4" t="s">
+        <v>626</v>
       </c>
       <c r="C70" t="s">
         <v>84</v>
@@ -4641,9 +6226,8 @@
       <c r="A71" s="2">
         <v>35166</v>
       </c>
-      <c r="B71" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35166</v>
+      <c r="B71" t="s">
+        <v>627</v>
       </c>
       <c r="C71" t="s">
         <v>85</v>
@@ -4677,9 +6261,8 @@
       <c r="A72" s="2">
         <v>35167</v>
       </c>
-      <c r="B72" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35167</v>
+      <c r="B72" s="4" t="s">
+        <v>628</v>
       </c>
       <c r="C72" t="s">
         <v>86</v>
@@ -4713,9 +6296,8 @@
       <c r="A73" s="2">
         <v>35168</v>
       </c>
-      <c r="B73" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35168</v>
+      <c r="B73" t="s">
+        <v>629</v>
       </c>
       <c r="C73" t="s">
         <v>87</v>
@@ -4749,9 +6331,8 @@
       <c r="A74" s="2">
         <v>35169</v>
       </c>
-      <c r="B74" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35169</v>
+      <c r="B74" s="4" t="s">
+        <v>630</v>
       </c>
       <c r="C74" t="s">
         <v>88</v>
@@ -4785,9 +6366,8 @@
       <c r="A75" s="2">
         <v>35170</v>
       </c>
-      <c r="B75" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35170</v>
+      <c r="B75" t="s">
+        <v>631</v>
       </c>
       <c r="C75" t="s">
         <v>89</v>
@@ -4821,9 +6401,8 @@
       <c r="A76" s="2">
         <v>35171</v>
       </c>
-      <c r="B76" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35171</v>
+      <c r="B76" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="C76" t="s">
         <v>90</v>
@@ -4857,9 +6436,8 @@
       <c r="A77" s="2">
         <v>35172</v>
       </c>
-      <c r="B77" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35172</v>
+      <c r="B77" t="s">
+        <v>633</v>
       </c>
       <c r="C77" t="s">
         <v>91</v>
@@ -4893,9 +6471,8 @@
       <c r="A78" s="2">
         <v>35173</v>
       </c>
-      <c r="B78" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35173</v>
+      <c r="B78" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="C78" t="s">
         <v>92</v>
@@ -4929,9 +6506,8 @@
       <c r="A79" s="2">
         <v>35174</v>
       </c>
-      <c r="B79" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35174</v>
+      <c r="B79" t="s">
+        <v>635</v>
       </c>
       <c r="C79" t="s">
         <v>93</v>
@@ -4965,9 +6541,8 @@
       <c r="A80" s="2">
         <v>35175</v>
       </c>
-      <c r="B80" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35175</v>
+      <c r="B80" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="C80" t="s">
         <v>94</v>
@@ -5001,9 +6576,8 @@
       <c r="A81" s="2">
         <v>35176</v>
       </c>
-      <c r="B81" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35176</v>
+      <c r="B81" t="s">
+        <v>637</v>
       </c>
       <c r="C81" t="s">
         <v>95</v>
@@ -5037,9 +6611,8 @@
       <c r="A82" s="2">
         <v>35177</v>
       </c>
-      <c r="B82" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35177</v>
+      <c r="B82" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="C82" t="s">
         <v>96</v>
@@ -5073,9 +6646,8 @@
       <c r="A83" s="2">
         <v>35178</v>
       </c>
-      <c r="B83" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35178</v>
+      <c r="B83" t="s">
+        <v>639</v>
       </c>
       <c r="C83" t="s">
         <v>97</v>
@@ -5109,9 +6681,8 @@
       <c r="A84" s="2">
         <v>35179</v>
       </c>
-      <c r="B84" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35179</v>
+      <c r="B84" s="4" t="s">
+        <v>640</v>
       </c>
       <c r="C84" t="s">
         <v>98</v>
@@ -5145,9 +6716,8 @@
       <c r="A85" s="2">
         <v>35180</v>
       </c>
-      <c r="B85" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35180</v>
+      <c r="B85" t="s">
+        <v>641</v>
       </c>
       <c r="C85" t="s">
         <v>99</v>
@@ -5181,9 +6751,8 @@
       <c r="A86" s="2">
         <v>35181</v>
       </c>
-      <c r="B86" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35181</v>
+      <c r="B86" s="4" t="s">
+        <v>642</v>
       </c>
       <c r="C86" t="s">
         <v>100</v>
@@ -5217,9 +6786,8 @@
       <c r="A87" s="2">
         <v>35182</v>
       </c>
-      <c r="B87" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35182</v>
+      <c r="B87" t="s">
+        <v>643</v>
       </c>
       <c r="C87" t="s">
         <v>101</v>
@@ -5253,9 +6821,8 @@
       <c r="A88" s="2">
         <v>35183</v>
       </c>
-      <c r="B88" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35183</v>
+      <c r="B88" s="4" t="s">
+        <v>644</v>
       </c>
       <c r="C88" t="s">
         <v>102</v>
@@ -5289,9 +6856,8 @@
       <c r="A89" s="2">
         <v>35184</v>
       </c>
-      <c r="B89" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35184</v>
+      <c r="B89" t="s">
+        <v>645</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
@@ -5325,9 +6891,8 @@
       <c r="A90" s="2">
         <v>35185</v>
       </c>
-      <c r="B90" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35185</v>
+      <c r="B90" s="4" t="s">
+        <v>646</v>
       </c>
       <c r="C90" t="s">
         <v>104</v>
@@ -5361,9 +6926,8 @@
       <c r="A91" s="2">
         <v>35186</v>
       </c>
-      <c r="B91" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35186</v>
+      <c r="B91" t="s">
+        <v>647</v>
       </c>
       <c r="C91" t="s">
         <v>105</v>
@@ -5397,9 +6961,8 @@
       <c r="A92" s="2">
         <v>35187</v>
       </c>
-      <c r="B92" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35187</v>
+      <c r="B92" s="4" t="s">
+        <v>648</v>
       </c>
       <c r="C92" t="s">
         <v>106</v>
@@ -5433,9 +6996,8 @@
       <c r="A93" s="2">
         <v>35188</v>
       </c>
-      <c r="B93" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35188</v>
+      <c r="B93" t="s">
+        <v>649</v>
       </c>
       <c r="C93" t="s">
         <v>107</v>
@@ -5469,9 +7031,8 @@
       <c r="A94" s="2">
         <v>35189</v>
       </c>
-      <c r="B94" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35189</v>
+      <c r="B94" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="C94" t="s">
         <v>108</v>
@@ -5505,9 +7066,8 @@
       <c r="A95" s="2">
         <v>35190</v>
       </c>
-      <c r="B95" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35190</v>
+      <c r="B95" t="s">
+        <v>651</v>
       </c>
       <c r="C95" t="s">
         <v>109</v>
@@ -5541,9 +7101,8 @@
       <c r="A96" s="2">
         <v>35191</v>
       </c>
-      <c r="B96" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35191</v>
+      <c r="B96" s="4" t="s">
+        <v>652</v>
       </c>
       <c r="C96" t="s">
         <v>110</v>
@@ -5577,9 +7136,8 @@
       <c r="A97" s="2">
         <v>35192</v>
       </c>
-      <c r="B97" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35192</v>
+      <c r="B97" t="s">
+        <v>653</v>
       </c>
       <c r="C97" t="s">
         <v>111</v>
@@ -5613,9 +7171,8 @@
       <c r="A98" s="2">
         <v>35193</v>
       </c>
-      <c r="B98" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35193</v>
+      <c r="B98" s="4" t="s">
+        <v>654</v>
       </c>
       <c r="C98" t="s">
         <v>112</v>
@@ -5649,9 +7206,8 @@
       <c r="A99" s="2">
         <v>35194</v>
       </c>
-      <c r="B99" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35194</v>
+      <c r="B99" t="s">
+        <v>655</v>
       </c>
       <c r="C99" t="s">
         <v>113</v>
@@ -5685,9 +7241,8 @@
       <c r="A100" s="2">
         <v>35195</v>
       </c>
-      <c r="B100" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35195</v>
+      <c r="B100" s="4" t="s">
+        <v>656</v>
       </c>
       <c r="C100" t="s">
         <v>114</v>
@@ -5721,9 +7276,8 @@
       <c r="A101" s="2">
         <v>35196</v>
       </c>
-      <c r="B101" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35196</v>
+      <c r="B101" t="s">
+        <v>657</v>
       </c>
       <c r="C101" t="s">
         <v>115</v>
@@ -5757,9 +7311,8 @@
       <c r="A102" s="2">
         <v>35197</v>
       </c>
-      <c r="B102" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35197</v>
+      <c r="B102" s="4" t="s">
+        <v>658</v>
       </c>
       <c r="C102" t="s">
         <v>116</v>
@@ -5793,9 +7346,8 @@
       <c r="A103" s="2">
         <v>35198</v>
       </c>
-      <c r="B103" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35198</v>
+      <c r="B103" t="s">
+        <v>659</v>
       </c>
       <c r="C103" t="s">
         <v>117</v>
@@ -5829,9 +7381,8 @@
       <c r="A104" s="2">
         <v>35199</v>
       </c>
-      <c r="B104" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35199</v>
+      <c r="B104" s="4" t="s">
+        <v>660</v>
       </c>
       <c r="C104" t="s">
         <v>118</v>
@@ -5865,9 +7416,8 @@
       <c r="A105" s="2">
         <v>35200</v>
       </c>
-      <c r="B105" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35200</v>
+      <c r="B105" t="s">
+        <v>661</v>
       </c>
       <c r="C105" t="s">
         <v>119</v>
@@ -5901,9 +7451,8 @@
       <c r="A106" s="2">
         <v>35201</v>
       </c>
-      <c r="B106" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35201</v>
+      <c r="B106" s="4" t="s">
+        <v>662</v>
       </c>
       <c r="C106" t="s">
         <v>120</v>
@@ -5937,9 +7486,8 @@
       <c r="A107" s="2">
         <v>35202</v>
       </c>
-      <c r="B107" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35202</v>
+      <c r="B107" t="s">
+        <v>663</v>
       </c>
       <c r="C107" t="s">
         <v>121</v>
@@ -5973,9 +7521,8 @@
       <c r="A108" s="2">
         <v>35203</v>
       </c>
-      <c r="B108" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35203</v>
+      <c r="B108" s="4" t="s">
+        <v>664</v>
       </c>
       <c r="C108" t="s">
         <v>122</v>
@@ -6009,9 +7556,8 @@
       <c r="A109" s="2">
         <v>35204</v>
       </c>
-      <c r="B109" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35204</v>
+      <c r="B109" t="s">
+        <v>665</v>
       </c>
       <c r="C109" t="s">
         <v>123</v>
@@ -6045,9 +7591,8 @@
       <c r="A110" s="2">
         <v>35205</v>
       </c>
-      <c r="B110" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35205</v>
+      <c r="B110" s="4" t="s">
+        <v>666</v>
       </c>
       <c r="C110" t="s">
         <v>124</v>
@@ -6081,9 +7626,8 @@
       <c r="A111" s="2">
         <v>35206</v>
       </c>
-      <c r="B111" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35206</v>
+      <c r="B111" t="s">
+        <v>667</v>
       </c>
       <c r="C111" t="s">
         <v>125</v>
@@ -6117,9 +7661,8 @@
       <c r="A112" s="2">
         <v>35207</v>
       </c>
-      <c r="B112" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35207</v>
+      <c r="B112" s="4" t="s">
+        <v>668</v>
       </c>
       <c r="C112" t="s">
         <v>126</v>
@@ -6153,9 +7696,8 @@
       <c r="A113" s="2">
         <v>35208</v>
       </c>
-      <c r="B113" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35208</v>
+      <c r="B113" t="s">
+        <v>669</v>
       </c>
       <c r="C113" t="s">
         <v>127</v>
@@ -6189,9 +7731,8 @@
       <c r="A114" s="2">
         <v>35209</v>
       </c>
-      <c r="B114" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35209</v>
+      <c r="B114" s="4" t="s">
+        <v>670</v>
       </c>
       <c r="C114" t="s">
         <v>128</v>
@@ -6225,9 +7766,8 @@
       <c r="A115" s="2">
         <v>35210</v>
       </c>
-      <c r="B115" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35210</v>
+      <c r="B115" t="s">
+        <v>671</v>
       </c>
       <c r="C115" t="s">
         <v>129</v>
@@ -6261,9 +7801,8 @@
       <c r="A116" s="2">
         <v>35211</v>
       </c>
-      <c r="B116" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35211</v>
+      <c r="B116" s="4" t="s">
+        <v>672</v>
       </c>
       <c r="C116" t="s">
         <v>130</v>
@@ -6297,9 +7836,8 @@
       <c r="A117" s="2">
         <v>35212</v>
       </c>
-      <c r="B117" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35212</v>
+      <c r="B117" t="s">
+        <v>673</v>
       </c>
       <c r="C117" t="s">
         <v>131</v>
@@ -6333,9 +7871,8 @@
       <c r="A118" s="2">
         <v>35213</v>
       </c>
-      <c r="B118" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35213</v>
+      <c r="B118" s="4" t="s">
+        <v>674</v>
       </c>
       <c r="C118" t="s">
         <v>132</v>
@@ -6369,9 +7906,8 @@
       <c r="A119" s="2">
         <v>35214</v>
       </c>
-      <c r="B119" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35214</v>
+      <c r="B119" t="s">
+        <v>675</v>
       </c>
       <c r="C119" t="s">
         <v>133</v>
@@ -6405,9 +7941,8 @@
       <c r="A120" s="2">
         <v>35215</v>
       </c>
-      <c r="B120" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35215</v>
+      <c r="B120" s="4" t="s">
+        <v>676</v>
       </c>
       <c r="C120" t="s">
         <v>134</v>
@@ -6441,9 +7976,8 @@
       <c r="A121" s="2">
         <v>35216</v>
       </c>
-      <c r="B121" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35216</v>
+      <c r="B121" t="s">
+        <v>677</v>
       </c>
       <c r="C121" t="s">
         <v>135</v>
@@ -6477,9 +8011,8 @@
       <c r="A122" s="2">
         <v>35217</v>
       </c>
-      <c r="B122" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35217</v>
+      <c r="B122" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="C122" t="s">
         <v>136</v>
@@ -6513,9 +8046,8 @@
       <c r="A123" s="2">
         <v>35218</v>
       </c>
-      <c r="B123" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35218</v>
+      <c r="B123" t="s">
+        <v>679</v>
       </c>
       <c r="C123" t="s">
         <v>137</v>
@@ -6549,9 +8081,8 @@
       <c r="A124" s="2">
         <v>35219</v>
       </c>
-      <c r="B124" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35219</v>
+      <c r="B124" s="4" t="s">
+        <v>680</v>
       </c>
       <c r="C124" t="s">
         <v>138</v>
@@ -6585,9 +8116,8 @@
       <c r="A125" s="2">
         <v>35220</v>
       </c>
-      <c r="B125" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35220</v>
+      <c r="B125" t="s">
+        <v>681</v>
       </c>
       <c r="C125" t="s">
         <v>139</v>
@@ -6621,9 +8151,8 @@
       <c r="A126" s="2">
         <v>35221</v>
       </c>
-      <c r="B126" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35221</v>
+      <c r="B126" s="4" t="s">
+        <v>682</v>
       </c>
       <c r="C126" t="s">
         <v>140</v>
@@ -6657,9 +8186,8 @@
       <c r="A127" s="2">
         <v>35222</v>
       </c>
-      <c r="B127" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35222</v>
+      <c r="B127" t="s">
+        <v>683</v>
       </c>
       <c r="C127" t="s">
         <v>141</v>
@@ -6693,9 +8221,8 @@
       <c r="A128" s="2">
         <v>35223</v>
       </c>
-      <c r="B128" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35223</v>
+      <c r="B128" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="C128" t="s">
         <v>142</v>
@@ -6729,9 +8256,8 @@
       <c r="A129" s="2">
         <v>35224</v>
       </c>
-      <c r="B129" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35224</v>
+      <c r="B129" t="s">
+        <v>685</v>
       </c>
       <c r="C129" t="s">
         <v>143</v>
@@ -6765,9 +8291,8 @@
       <c r="A130" s="2">
         <v>35225</v>
       </c>
-      <c r="B130" t="str">
-        <f t="shared" si="1"/>
-        <v>Prchile-35225</v>
+      <c r="B130" s="4" t="s">
+        <v>686</v>
       </c>
       <c r="C130" t="s">
         <v>144</v>
@@ -6801,9 +8326,8 @@
       <c r="A131" s="2">
         <v>35226</v>
       </c>
-      <c r="B131" t="str">
-        <f t="shared" ref="B131:B194" si="2">$B$1&amp;"-"&amp;A131</f>
-        <v>Prchile-35226</v>
+      <c r="B131" t="s">
+        <v>687</v>
       </c>
       <c r="C131" t="s">
         <v>145</v>
@@ -6837,9 +8361,8 @@
       <c r="A132" s="2">
         <v>35227</v>
       </c>
-      <c r="B132" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35227</v>
+      <c r="B132" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="C132" t="s">
         <v>146</v>
@@ -6873,9 +8396,8 @@
       <c r="A133" s="2">
         <v>35228</v>
       </c>
-      <c r="B133" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35228</v>
+      <c r="B133" t="s">
+        <v>689</v>
       </c>
       <c r="C133" t="s">
         <v>147</v>
@@ -6909,9 +8431,8 @@
       <c r="A134" s="2">
         <v>35229</v>
       </c>
-      <c r="B134" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35229</v>
+      <c r="B134" s="4" t="s">
+        <v>690</v>
       </c>
       <c r="C134" t="s">
         <v>148</v>
@@ -6945,9 +8466,8 @@
       <c r="A135" s="2">
         <v>35230</v>
       </c>
-      <c r="B135" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35230</v>
+      <c r="B135" t="s">
+        <v>691</v>
       </c>
       <c r="C135" t="s">
         <v>149</v>
@@ -6981,9 +8501,8 @@
       <c r="A136" s="2">
         <v>35231</v>
       </c>
-      <c r="B136" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35231</v>
+      <c r="B136" s="4" t="s">
+        <v>692</v>
       </c>
       <c r="C136" t="s">
         <v>150</v>
@@ -7017,9 +8536,8 @@
       <c r="A137" s="2">
         <v>35232</v>
       </c>
-      <c r="B137" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35232</v>
+      <c r="B137" t="s">
+        <v>693</v>
       </c>
       <c r="C137" t="s">
         <v>151</v>
@@ -7053,9 +8571,8 @@
       <c r="A138" s="2">
         <v>35233</v>
       </c>
-      <c r="B138" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35233</v>
+      <c r="B138" s="4" t="s">
+        <v>694</v>
       </c>
       <c r="C138" t="s">
         <v>152</v>
@@ -7089,9 +8606,8 @@
       <c r="A139" s="2">
         <v>35234</v>
       </c>
-      <c r="B139" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35234</v>
+      <c r="B139" t="s">
+        <v>695</v>
       </c>
       <c r="C139" t="s">
         <v>153</v>
@@ -7125,9 +8641,8 @@
       <c r="A140" s="2">
         <v>35235</v>
       </c>
-      <c r="B140" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35235</v>
+      <c r="B140" s="4" t="s">
+        <v>696</v>
       </c>
       <c r="C140" t="s">
         <v>154</v>
@@ -7161,9 +8676,8 @@
       <c r="A141" s="2">
         <v>35236</v>
       </c>
-      <c r="B141" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35236</v>
+      <c r="B141" t="s">
+        <v>697</v>
       </c>
       <c r="C141" t="s">
         <v>155</v>
@@ -7197,9 +8711,8 @@
       <c r="A142" s="2">
         <v>35237</v>
       </c>
-      <c r="B142" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35237</v>
+      <c r="B142" s="4" t="s">
+        <v>698</v>
       </c>
       <c r="C142" t="s">
         <v>156</v>
@@ -7233,9 +8746,8 @@
       <c r="A143" s="2">
         <v>35238</v>
       </c>
-      <c r="B143" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35238</v>
+      <c r="B143" t="s">
+        <v>699</v>
       </c>
       <c r="C143" t="s">
         <v>157</v>
@@ -7269,9 +8781,8 @@
       <c r="A144" s="2">
         <v>35239</v>
       </c>
-      <c r="B144" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35239</v>
+      <c r="B144" s="4" t="s">
+        <v>700</v>
       </c>
       <c r="C144" t="s">
         <v>158</v>
@@ -7305,9 +8816,8 @@
       <c r="A145" s="2">
         <v>35240</v>
       </c>
-      <c r="B145" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35240</v>
+      <c r="B145" t="s">
+        <v>701</v>
       </c>
       <c r="C145" t="s">
         <v>159</v>
@@ -7341,9 +8851,8 @@
       <c r="A146" s="2">
         <v>35241</v>
       </c>
-      <c r="B146" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35241</v>
+      <c r="B146" s="4" t="s">
+        <v>702</v>
       </c>
       <c r="C146" t="s">
         <v>160</v>
@@ -7377,9 +8886,8 @@
       <c r="A147" s="2">
         <v>35242</v>
       </c>
-      <c r="B147" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35242</v>
+      <c r="B147" t="s">
+        <v>703</v>
       </c>
       <c r="C147" t="s">
         <v>161</v>
@@ -7413,9 +8921,8 @@
       <c r="A148" s="2">
         <v>35243</v>
       </c>
-      <c r="B148" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35243</v>
+      <c r="B148" s="4" t="s">
+        <v>704</v>
       </c>
       <c r="C148" t="s">
         <v>162</v>
@@ -7449,9 +8956,8 @@
       <c r="A149" s="2">
         <v>35244</v>
       </c>
-      <c r="B149" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35244</v>
+      <c r="B149" t="s">
+        <v>705</v>
       </c>
       <c r="C149" t="s">
         <v>163</v>
@@ -7485,9 +8991,8 @@
       <c r="A150" s="2">
         <v>35245</v>
       </c>
-      <c r="B150" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35245</v>
+      <c r="B150" s="4" t="s">
+        <v>706</v>
       </c>
       <c r="C150" t="s">
         <v>164</v>
@@ -7521,9 +9026,8 @@
       <c r="A151" s="2">
         <v>35246</v>
       </c>
-      <c r="B151" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35246</v>
+      <c r="B151" t="s">
+        <v>707</v>
       </c>
       <c r="C151" t="s">
         <v>165</v>
@@ -7557,9 +9061,8 @@
       <c r="A152" s="2">
         <v>35247</v>
       </c>
-      <c r="B152" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35247</v>
+      <c r="B152" s="4" t="s">
+        <v>708</v>
       </c>
       <c r="C152" t="s">
         <v>166</v>
@@ -7593,9 +9096,8 @@
       <c r="A153" s="2">
         <v>35248</v>
       </c>
-      <c r="B153" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35248</v>
+      <c r="B153" t="s">
+        <v>709</v>
       </c>
       <c r="C153" t="s">
         <v>167</v>
@@ -7629,9 +9131,8 @@
       <c r="A154" s="2">
         <v>35249</v>
       </c>
-      <c r="B154" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35249</v>
+      <c r="B154" s="4" t="s">
+        <v>710</v>
       </c>
       <c r="C154" t="s">
         <v>168</v>
@@ -7665,9 +9166,8 @@
       <c r="A155" s="2">
         <v>35250</v>
       </c>
-      <c r="B155" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35250</v>
+      <c r="B155" t="s">
+        <v>711</v>
       </c>
       <c r="C155" t="s">
         <v>169</v>
@@ -7701,9 +9201,8 @@
       <c r="A156" s="2">
         <v>35251</v>
       </c>
-      <c r="B156" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35251</v>
+      <c r="B156" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="C156" t="s">
         <v>170</v>
@@ -7737,9 +9236,8 @@
       <c r="A157" s="2">
         <v>35252</v>
       </c>
-      <c r="B157" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35252</v>
+      <c r="B157" t="s">
+        <v>713</v>
       </c>
       <c r="C157" t="s">
         <v>171</v>
@@ -7773,9 +9271,8 @@
       <c r="A158" s="2">
         <v>35253</v>
       </c>
-      <c r="B158" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35253</v>
+      <c r="B158" s="4" t="s">
+        <v>714</v>
       </c>
       <c r="C158" t="s">
         <v>172</v>
@@ -7809,9 +9306,8 @@
       <c r="A159" s="2">
         <v>35254</v>
       </c>
-      <c r="B159" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35254</v>
+      <c r="B159" t="s">
+        <v>715</v>
       </c>
       <c r="C159" t="s">
         <v>173</v>
@@ -7845,9 +9341,8 @@
       <c r="A160" s="2">
         <v>35255</v>
       </c>
-      <c r="B160" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35255</v>
+      <c r="B160" s="4" t="s">
+        <v>716</v>
       </c>
       <c r="C160" t="s">
         <v>174</v>
@@ -7881,9 +9376,8 @@
       <c r="A161" s="2">
         <v>35256</v>
       </c>
-      <c r="B161" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35256</v>
+      <c r="B161" t="s">
+        <v>717</v>
       </c>
       <c r="C161" t="s">
         <v>175</v>
@@ -7917,9 +9411,8 @@
       <c r="A162" s="2">
         <v>35257</v>
       </c>
-      <c r="B162" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35257</v>
+      <c r="B162" s="4" t="s">
+        <v>718</v>
       </c>
       <c r="C162" t="s">
         <v>176</v>
@@ -7953,9 +9446,8 @@
       <c r="A163" s="2">
         <v>35258</v>
       </c>
-      <c r="B163" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35258</v>
+      <c r="B163" t="s">
+        <v>719</v>
       </c>
       <c r="C163" t="s">
         <v>177</v>
@@ -7989,9 +9481,8 @@
       <c r="A164" s="2">
         <v>35259</v>
       </c>
-      <c r="B164" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35259</v>
+      <c r="B164" s="4" t="s">
+        <v>720</v>
       </c>
       <c r="C164" t="s">
         <v>178</v>
@@ -8025,9 +9516,8 @@
       <c r="A165" s="2">
         <v>35260</v>
       </c>
-      <c r="B165" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35260</v>
+      <c r="B165" t="s">
+        <v>721</v>
       </c>
       <c r="C165" t="s">
         <v>179</v>
@@ -8061,9 +9551,8 @@
       <c r="A166" s="2">
         <v>35261</v>
       </c>
-      <c r="B166" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35261</v>
+      <c r="B166" s="4" t="s">
+        <v>722</v>
       </c>
       <c r="C166" t="s">
         <v>180</v>
@@ -8097,9 +9586,8 @@
       <c r="A167" s="2">
         <v>35262</v>
       </c>
-      <c r="B167" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35262</v>
+      <c r="B167" t="s">
+        <v>723</v>
       </c>
       <c r="C167" t="s">
         <v>181</v>
@@ -8133,9 +9621,8 @@
       <c r="A168" s="2">
         <v>35263</v>
       </c>
-      <c r="B168" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35263</v>
+      <c r="B168" s="4" t="s">
+        <v>724</v>
       </c>
       <c r="C168" t="s">
         <v>182</v>
@@ -8169,9 +9656,8 @@
       <c r="A169" s="2">
         <v>35264</v>
       </c>
-      <c r="B169" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35264</v>
+      <c r="B169" t="s">
+        <v>725</v>
       </c>
       <c r="C169" t="s">
         <v>183</v>
@@ -8205,9 +9691,8 @@
       <c r="A170" s="2">
         <v>35265</v>
       </c>
-      <c r="B170" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35265</v>
+      <c r="B170" s="4" t="s">
+        <v>726</v>
       </c>
       <c r="C170" t="s">
         <v>184</v>
@@ -8241,9 +9726,8 @@
       <c r="A171" s="2">
         <v>35266</v>
       </c>
-      <c r="B171" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35266</v>
+      <c r="B171" t="s">
+        <v>727</v>
       </c>
       <c r="C171" t="s">
         <v>185</v>
@@ -8277,9 +9761,8 @@
       <c r="A172" s="2">
         <v>35267</v>
       </c>
-      <c r="B172" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35267</v>
+      <c r="B172" s="4" t="s">
+        <v>728</v>
       </c>
       <c r="C172" t="s">
         <v>186</v>
@@ -8313,9 +9796,8 @@
       <c r="A173" s="2">
         <v>35268</v>
       </c>
-      <c r="B173" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35268</v>
+      <c r="B173" t="s">
+        <v>729</v>
       </c>
       <c r="C173" t="s">
         <v>187</v>
@@ -8349,9 +9831,8 @@
       <c r="A174" s="2">
         <v>35269</v>
       </c>
-      <c r="B174" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35269</v>
+      <c r="B174" s="4" t="s">
+        <v>730</v>
       </c>
       <c r="C174" t="s">
         <v>188</v>
@@ -8385,9 +9866,8 @@
       <c r="A175" s="2">
         <v>35270</v>
       </c>
-      <c r="B175" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35270</v>
+      <c r="B175" t="s">
+        <v>731</v>
       </c>
       <c r="C175" t="s">
         <v>189</v>
@@ -8421,9 +9901,8 @@
       <c r="A176" s="2">
         <v>35271</v>
       </c>
-      <c r="B176" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35271</v>
+      <c r="B176" s="4" t="s">
+        <v>732</v>
       </c>
       <c r="C176" t="s">
         <v>190</v>
@@ -8457,9 +9936,8 @@
       <c r="A177" s="2">
         <v>35272</v>
       </c>
-      <c r="B177" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35272</v>
+      <c r="B177" t="s">
+        <v>733</v>
       </c>
       <c r="C177" t="s">
         <v>191</v>
@@ -8493,9 +9971,8 @@
       <c r="A178" s="2">
         <v>35273</v>
       </c>
-      <c r="B178" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35273</v>
+      <c r="B178" s="4" t="s">
+        <v>734</v>
       </c>
       <c r="C178" t="s">
         <v>192</v>
@@ -8529,9 +10006,8 @@
       <c r="A179" s="2">
         <v>35274</v>
       </c>
-      <c r="B179" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35274</v>
+      <c r="B179" t="s">
+        <v>735</v>
       </c>
       <c r="C179" t="s">
         <v>193</v>
@@ -8565,9 +10041,8 @@
       <c r="A180" s="2">
         <v>35275</v>
       </c>
-      <c r="B180" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35275</v>
+      <c r="B180" s="4" t="s">
+        <v>736</v>
       </c>
       <c r="C180" t="s">
         <v>194</v>
@@ -8601,9 +10076,8 @@
       <c r="A181" s="2">
         <v>35276</v>
       </c>
-      <c r="B181" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35276</v>
+      <c r="B181" t="s">
+        <v>737</v>
       </c>
       <c r="C181" t="s">
         <v>195</v>
@@ -8637,9 +10111,8 @@
       <c r="A182" s="2">
         <v>35277</v>
       </c>
-      <c r="B182" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35277</v>
+      <c r="B182" s="4" t="s">
+        <v>738</v>
       </c>
       <c r="C182" t="s">
         <v>196</v>
@@ -8673,9 +10146,8 @@
       <c r="A183" s="2">
         <v>35278</v>
       </c>
-      <c r="B183" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35278</v>
+      <c r="B183" t="s">
+        <v>739</v>
       </c>
       <c r="C183" t="s">
         <v>197</v>
@@ -8709,9 +10181,8 @@
       <c r="A184" s="2">
         <v>35279</v>
       </c>
-      <c r="B184" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35279</v>
+      <c r="B184" s="4" t="s">
+        <v>740</v>
       </c>
       <c r="C184" t="s">
         <v>198</v>
@@ -8745,9 +10216,8 @@
       <c r="A185" s="2">
         <v>35280</v>
       </c>
-      <c r="B185" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35280</v>
+      <c r="B185" t="s">
+        <v>741</v>
       </c>
       <c r="C185" t="s">
         <v>199</v>
@@ -8781,9 +10251,8 @@
       <c r="A186" s="2">
         <v>35281</v>
       </c>
-      <c r="B186" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35281</v>
+      <c r="B186" s="4" t="s">
+        <v>742</v>
       </c>
       <c r="C186" t="s">
         <v>200</v>
@@ -8817,9 +10286,8 @@
       <c r="A187" s="2">
         <v>35282</v>
       </c>
-      <c r="B187" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35282</v>
+      <c r="B187" t="s">
+        <v>743</v>
       </c>
       <c r="C187" t="s">
         <v>201</v>
@@ -8853,9 +10321,8 @@
       <c r="A188" s="2">
         <v>35283</v>
       </c>
-      <c r="B188" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35283</v>
+      <c r="B188" s="4" t="s">
+        <v>744</v>
       </c>
       <c r="C188" t="s">
         <v>202</v>
@@ -8889,9 +10356,8 @@
       <c r="A189" s="2">
         <v>35284</v>
       </c>
-      <c r="B189" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35284</v>
+      <c r="B189" t="s">
+        <v>745</v>
       </c>
       <c r="C189" t="s">
         <v>203</v>
@@ -8925,9 +10391,8 @@
       <c r="A190" s="2">
         <v>35285</v>
       </c>
-      <c r="B190" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35285</v>
+      <c r="B190" s="4" t="s">
+        <v>746</v>
       </c>
       <c r="C190" t="s">
         <v>204</v>
@@ -8961,9 +10426,8 @@
       <c r="A191" s="2">
         <v>35286</v>
       </c>
-      <c r="B191" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35286</v>
+      <c r="B191" t="s">
+        <v>747</v>
       </c>
       <c r="C191" t="s">
         <v>205</v>
@@ -8997,9 +10461,8 @@
       <c r="A192" s="2">
         <v>35287</v>
       </c>
-      <c r="B192" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35287</v>
+      <c r="B192" s="4" t="s">
+        <v>748</v>
       </c>
       <c r="C192" t="s">
         <v>206</v>
@@ -9033,9 +10496,8 @@
       <c r="A193" s="2">
         <v>35288</v>
       </c>
-      <c r="B193" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35288</v>
+      <c r="B193" t="s">
+        <v>749</v>
       </c>
       <c r="C193" t="s">
         <v>207</v>
@@ -9069,9 +10531,8 @@
       <c r="A194" s="2">
         <v>35289</v>
       </c>
-      <c r="B194" t="str">
-        <f t="shared" si="2"/>
-        <v>Prchile-35289</v>
+      <c r="B194" s="4" t="s">
+        <v>750</v>
       </c>
       <c r="C194" t="s">
         <v>208</v>
@@ -9105,9 +10566,8 @@
       <c r="A195" s="2">
         <v>35290</v>
       </c>
-      <c r="B195" t="str">
-        <f t="shared" ref="B195:B258" si="3">$B$1&amp;"-"&amp;A195</f>
-        <v>Prchile-35290</v>
+      <c r="B195" t="s">
+        <v>751</v>
       </c>
       <c r="C195" t="s">
         <v>209</v>
@@ -9141,9 +10601,8 @@
       <c r="A196" s="2">
         <v>35291</v>
       </c>
-      <c r="B196" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35291</v>
+      <c r="B196" s="4" t="s">
+        <v>752</v>
       </c>
       <c r="C196" t="s">
         <v>210</v>
@@ -9177,9 +10636,8 @@
       <c r="A197" s="2">
         <v>35292</v>
       </c>
-      <c r="B197" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35292</v>
+      <c r="B197" t="s">
+        <v>753</v>
       </c>
       <c r="C197" t="s">
         <v>211</v>
@@ -9213,9 +10671,8 @@
       <c r="A198" s="2">
         <v>35293</v>
       </c>
-      <c r="B198" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35293</v>
+      <c r="B198" s="4" t="s">
+        <v>754</v>
       </c>
       <c r="C198" t="s">
         <v>212</v>
@@ -9249,9 +10706,8 @@
       <c r="A199" s="2">
         <v>35294</v>
       </c>
-      <c r="B199" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35294</v>
+      <c r="B199" t="s">
+        <v>755</v>
       </c>
       <c r="C199" t="s">
         <v>213</v>
@@ -9285,9 +10741,8 @@
       <c r="A200" s="2">
         <v>35295</v>
       </c>
-      <c r="B200" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35295</v>
+      <c r="B200" s="4" t="s">
+        <v>756</v>
       </c>
       <c r="C200" t="s">
         <v>214</v>
@@ -9321,9 +10776,8 @@
       <c r="A201" s="2">
         <v>35296</v>
       </c>
-      <c r="B201" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35296</v>
+      <c r="B201" t="s">
+        <v>757</v>
       </c>
       <c r="C201" t="s">
         <v>215</v>
@@ -9357,9 +10811,8 @@
       <c r="A202" s="2">
         <v>35297</v>
       </c>
-      <c r="B202" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35297</v>
+      <c r="B202" s="4" t="s">
+        <v>758</v>
       </c>
       <c r="C202" t="s">
         <v>216</v>
@@ -9393,9 +10846,8 @@
       <c r="A203" s="2">
         <v>35298</v>
       </c>
-      <c r="B203" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35298</v>
+      <c r="B203" t="s">
+        <v>759</v>
       </c>
       <c r="C203" t="s">
         <v>217</v>
@@ -9429,9 +10881,8 @@
       <c r="A204" s="2">
         <v>35299</v>
       </c>
-      <c r="B204" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35299</v>
+      <c r="B204" s="4" t="s">
+        <v>760</v>
       </c>
       <c r="C204" t="s">
         <v>218</v>
@@ -9465,9 +10916,8 @@
       <c r="A205" s="2">
         <v>35300</v>
       </c>
-      <c r="B205" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35300</v>
+      <c r="B205" t="s">
+        <v>761</v>
       </c>
       <c r="C205" t="s">
         <v>219</v>
@@ -9501,9 +10951,8 @@
       <c r="A206" s="2">
         <v>35301</v>
       </c>
-      <c r="B206" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35301</v>
+      <c r="B206" s="4" t="s">
+        <v>762</v>
       </c>
       <c r="C206" t="s">
         <v>220</v>
@@ -9537,9 +10986,8 @@
       <c r="A207" s="2">
         <v>35302</v>
       </c>
-      <c r="B207" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35302</v>
+      <c r="B207" t="s">
+        <v>763</v>
       </c>
       <c r="C207" t="s">
         <v>221</v>
@@ -9573,9 +11021,8 @@
       <c r="A208" s="2">
         <v>35303</v>
       </c>
-      <c r="B208" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35303</v>
+      <c r="B208" s="4" t="s">
+        <v>764</v>
       </c>
       <c r="C208" t="s">
         <v>222</v>
@@ -9609,9 +11056,8 @@
       <c r="A209" s="2">
         <v>35304</v>
       </c>
-      <c r="B209" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35304</v>
+      <c r="B209" t="s">
+        <v>765</v>
       </c>
       <c r="C209" t="s">
         <v>223</v>
@@ -9645,9 +11091,8 @@
       <c r="A210" s="2">
         <v>35305</v>
       </c>
-      <c r="B210" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35305</v>
+      <c r="B210" s="4" t="s">
+        <v>766</v>
       </c>
       <c r="C210" t="s">
         <v>224</v>
@@ -9681,9 +11126,8 @@
       <c r="A211" s="2">
         <v>35306</v>
       </c>
-      <c r="B211" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35306</v>
+      <c r="B211" t="s">
+        <v>767</v>
       </c>
       <c r="C211" t="s">
         <v>225</v>
@@ -9717,9 +11161,8 @@
       <c r="A212" s="2">
         <v>35307</v>
       </c>
-      <c r="B212" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35307</v>
+      <c r="B212" s="4" t="s">
+        <v>768</v>
       </c>
       <c r="C212" t="s">
         <v>226</v>
@@ -9753,9 +11196,8 @@
       <c r="A213" s="2">
         <v>35308</v>
       </c>
-      <c r="B213" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35308</v>
+      <c r="B213" t="s">
+        <v>769</v>
       </c>
       <c r="C213" t="s">
         <v>227</v>
@@ -9789,9 +11231,8 @@
       <c r="A214" s="2">
         <v>35309</v>
       </c>
-      <c r="B214" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35309</v>
+      <c r="B214" s="4" t="s">
+        <v>770</v>
       </c>
       <c r="C214" t="s">
         <v>228</v>
@@ -9825,9 +11266,8 @@
       <c r="A215" s="2">
         <v>35310</v>
       </c>
-      <c r="B215" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35310</v>
+      <c r="B215" t="s">
+        <v>771</v>
       </c>
       <c r="C215" t="s">
         <v>229</v>
@@ -9861,9 +11301,8 @@
       <c r="A216" s="2">
         <v>35311</v>
       </c>
-      <c r="B216" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35311</v>
+      <c r="B216" s="4" t="s">
+        <v>772</v>
       </c>
       <c r="C216" t="s">
         <v>230</v>
@@ -9897,9 +11336,8 @@
       <c r="A217" s="2">
         <v>35312</v>
       </c>
-      <c r="B217" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35312</v>
+      <c r="B217" t="s">
+        <v>773</v>
       </c>
       <c r="C217" t="s">
         <v>231</v>
@@ -9933,9 +11371,8 @@
       <c r="A218" s="2">
         <v>35313</v>
       </c>
-      <c r="B218" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35313</v>
+      <c r="B218" s="4" t="s">
+        <v>774</v>
       </c>
       <c r="C218" t="s">
         <v>232</v>
@@ -9969,9 +11406,8 @@
       <c r="A219" s="2">
         <v>35314</v>
       </c>
-      <c r="B219" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35314</v>
+      <c r="B219" t="s">
+        <v>775</v>
       </c>
       <c r="C219" t="s">
         <v>233</v>
@@ -10005,9 +11441,8 @@
       <c r="A220" s="2">
         <v>35315</v>
       </c>
-      <c r="B220" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35315</v>
+      <c r="B220" s="4" t="s">
+        <v>776</v>
       </c>
       <c r="C220" t="s">
         <v>234</v>
@@ -10041,9 +11476,8 @@
       <c r="A221" s="2">
         <v>35316</v>
       </c>
-      <c r="B221" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35316</v>
+      <c r="B221" t="s">
+        <v>777</v>
       </c>
       <c r="C221" t="s">
         <v>235</v>
@@ -10077,9 +11511,8 @@
       <c r="A222" s="2">
         <v>35317</v>
       </c>
-      <c r="B222" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35317</v>
+      <c r="B222" s="4" t="s">
+        <v>778</v>
       </c>
       <c r="C222" t="s">
         <v>236</v>
@@ -10113,9 +11546,8 @@
       <c r="A223" s="2">
         <v>35318</v>
       </c>
-      <c r="B223" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35318</v>
+      <c r="B223" t="s">
+        <v>779</v>
       </c>
       <c r="C223" t="s">
         <v>237</v>
@@ -10149,9 +11581,8 @@
       <c r="A224" s="2">
         <v>35319</v>
       </c>
-      <c r="B224" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35319</v>
+      <c r="B224" s="4" t="s">
+        <v>780</v>
       </c>
       <c r="C224" t="s">
         <v>238</v>
@@ -10185,9 +11616,8 @@
       <c r="A225" s="2">
         <v>35320</v>
       </c>
-      <c r="B225" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35320</v>
+      <c r="B225" t="s">
+        <v>781</v>
       </c>
       <c r="C225" t="s">
         <v>239</v>
@@ -10221,9 +11651,8 @@
       <c r="A226" s="2">
         <v>35321</v>
       </c>
-      <c r="B226" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35321</v>
+      <c r="B226" s="4" t="s">
+        <v>782</v>
       </c>
       <c r="C226" t="s">
         <v>240</v>
@@ -10257,9 +11686,8 @@
       <c r="A227" s="2">
         <v>35322</v>
       </c>
-      <c r="B227" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35322</v>
+      <c r="B227" t="s">
+        <v>783</v>
       </c>
       <c r="C227" t="s">
         <v>241</v>
@@ -10293,9 +11721,8 @@
       <c r="A228" s="2">
         <v>35323</v>
       </c>
-      <c r="B228" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35323</v>
+      <c r="B228" s="4" t="s">
+        <v>784</v>
       </c>
       <c r="C228" t="s">
         <v>242</v>
@@ -10329,9 +11756,8 @@
       <c r="A229" s="2">
         <v>35324</v>
       </c>
-      <c r="B229" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35324</v>
+      <c r="B229" t="s">
+        <v>785</v>
       </c>
       <c r="C229" t="s">
         <v>243</v>
@@ -10365,9 +11791,8 @@
       <c r="A230" s="2">
         <v>35325</v>
       </c>
-      <c r="B230" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35325</v>
+      <c r="B230" s="4" t="s">
+        <v>786</v>
       </c>
       <c r="C230" t="s">
         <v>244</v>
@@ -10401,9 +11826,8 @@
       <c r="A231" s="2">
         <v>35326</v>
       </c>
-      <c r="B231" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35326</v>
+      <c r="B231" t="s">
+        <v>787</v>
       </c>
       <c r="C231" t="s">
         <v>245</v>
@@ -10437,9 +11861,8 @@
       <c r="A232" s="2">
         <v>35327</v>
       </c>
-      <c r="B232" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35327</v>
+      <c r="B232" s="4" t="s">
+        <v>788</v>
       </c>
       <c r="C232" t="s">
         <v>246</v>
@@ -10473,9 +11896,8 @@
       <c r="A233" s="2">
         <v>35328</v>
       </c>
-      <c r="B233" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35328</v>
+      <c r="B233" t="s">
+        <v>789</v>
       </c>
       <c r="C233" t="s">
         <v>247</v>
@@ -10509,9 +11931,8 @@
       <c r="A234" s="2">
         <v>35329</v>
       </c>
-      <c r="B234" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35329</v>
+      <c r="B234" s="4" t="s">
+        <v>790</v>
       </c>
       <c r="C234" t="s">
         <v>248</v>
@@ -10545,9 +11966,8 @@
       <c r="A235" s="2">
         <v>35330</v>
       </c>
-      <c r="B235" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35330</v>
+      <c r="B235" t="s">
+        <v>791</v>
       </c>
       <c r="C235" t="s">
         <v>249</v>
@@ -10581,9 +12001,8 @@
       <c r="A236" s="2">
         <v>35331</v>
       </c>
-      <c r="B236" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35331</v>
+      <c r="B236" s="4" t="s">
+        <v>792</v>
       </c>
       <c r="C236" t="s">
         <v>250</v>
@@ -10617,9 +12036,8 @@
       <c r="A237" s="2">
         <v>35332</v>
       </c>
-      <c r="B237" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35332</v>
+      <c r="B237" t="s">
+        <v>793</v>
       </c>
       <c r="C237" t="s">
         <v>251</v>
@@ -10653,9 +12071,8 @@
       <c r="A238" s="2">
         <v>35333</v>
       </c>
-      <c r="B238" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35333</v>
+      <c r="B238" s="4" t="s">
+        <v>794</v>
       </c>
       <c r="C238" t="s">
         <v>252</v>
@@ -10689,9 +12106,8 @@
       <c r="A239" s="2">
         <v>35334</v>
       </c>
-      <c r="B239" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35334</v>
+      <c r="B239" t="s">
+        <v>795</v>
       </c>
       <c r="C239" t="s">
         <v>253</v>
@@ -10725,9 +12141,8 @@
       <c r="A240" s="2">
         <v>35335</v>
       </c>
-      <c r="B240" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35335</v>
+      <c r="B240" s="4" t="s">
+        <v>796</v>
       </c>
       <c r="C240" t="s">
         <v>254</v>
@@ -10761,9 +12176,8 @@
       <c r="A241" s="2">
         <v>35336</v>
       </c>
-      <c r="B241" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35336</v>
+      <c r="B241" t="s">
+        <v>797</v>
       </c>
       <c r="C241" t="s">
         <v>255</v>
@@ -10797,9 +12211,8 @@
       <c r="A242" s="2">
         <v>35337</v>
       </c>
-      <c r="B242" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35337</v>
+      <c r="B242" s="4" t="s">
+        <v>798</v>
       </c>
       <c r="C242" t="s">
         <v>256</v>
@@ -10833,9 +12246,8 @@
       <c r="A243" s="2">
         <v>35338</v>
       </c>
-      <c r="B243" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35338</v>
+      <c r="B243" t="s">
+        <v>799</v>
       </c>
       <c r="C243" t="s">
         <v>257</v>
@@ -10869,9 +12281,8 @@
       <c r="A244" s="2">
         <v>35339</v>
       </c>
-      <c r="B244" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35339</v>
+      <c r="B244" s="4" t="s">
+        <v>800</v>
       </c>
       <c r="C244" t="s">
         <v>258</v>
@@ -10905,9 +12316,8 @@
       <c r="A245" s="2">
         <v>35340</v>
       </c>
-      <c r="B245" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35340</v>
+      <c r="B245" t="s">
+        <v>801</v>
       </c>
       <c r="C245" t="s">
         <v>259</v>
@@ -10941,9 +12351,8 @@
       <c r="A246" s="2">
         <v>35341</v>
       </c>
-      <c r="B246" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35341</v>
+      <c r="B246" s="4" t="s">
+        <v>802</v>
       </c>
       <c r="C246" t="s">
         <v>260</v>
@@ -10977,9 +12386,8 @@
       <c r="A247" s="2">
         <v>35342</v>
       </c>
-      <c r="B247" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35342</v>
+      <c r="B247" t="s">
+        <v>803</v>
       </c>
       <c r="C247" t="s">
         <v>261</v>
@@ -11013,9 +12421,8 @@
       <c r="A248" s="2">
         <v>35343</v>
       </c>
-      <c r="B248" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35343</v>
+      <c r="B248" s="4" t="s">
+        <v>804</v>
       </c>
       <c r="C248" t="s">
         <v>262</v>
@@ -11049,9 +12456,8 @@
       <c r="A249" s="2">
         <v>35344</v>
       </c>
-      <c r="B249" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35344</v>
+      <c r="B249" t="s">
+        <v>805</v>
       </c>
       <c r="C249" t="s">
         <v>263</v>
@@ -11085,9 +12491,8 @@
       <c r="A250" s="2">
         <v>35345</v>
       </c>
-      <c r="B250" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35345</v>
+      <c r="B250" s="4" t="s">
+        <v>806</v>
       </c>
       <c r="C250" t="s">
         <v>264</v>
@@ -11121,9 +12526,8 @@
       <c r="A251" s="2">
         <v>35346</v>
       </c>
-      <c r="B251" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35346</v>
+      <c r="B251" t="s">
+        <v>807</v>
       </c>
       <c r="C251" t="s">
         <v>265</v>
@@ -11157,9 +12561,8 @@
       <c r="A252" s="2">
         <v>35347</v>
       </c>
-      <c r="B252" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35347</v>
+      <c r="B252" s="4" t="s">
+        <v>808</v>
       </c>
       <c r="C252" t="s">
         <v>266</v>
@@ -11193,9 +12596,8 @@
       <c r="A253" s="2">
         <v>35348</v>
       </c>
-      <c r="B253" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35348</v>
+      <c r="B253" t="s">
+        <v>809</v>
       </c>
       <c r="C253" t="s">
         <v>267</v>
@@ -11229,9 +12631,8 @@
       <c r="A254" s="2">
         <v>35349</v>
       </c>
-      <c r="B254" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35349</v>
+      <c r="B254" s="4" t="s">
+        <v>810</v>
       </c>
       <c r="C254" t="s">
         <v>268</v>
@@ -11265,9 +12666,8 @@
       <c r="A255" s="2">
         <v>35350</v>
       </c>
-      <c r="B255" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35350</v>
+      <c r="B255" t="s">
+        <v>811</v>
       </c>
       <c r="C255" t="s">
         <v>269</v>
@@ -11301,9 +12701,8 @@
       <c r="A256" s="2">
         <v>35351</v>
       </c>
-      <c r="B256" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35351</v>
+      <c r="B256" s="4" t="s">
+        <v>812</v>
       </c>
       <c r="C256" t="s">
         <v>270</v>
@@ -11337,9 +12736,8 @@
       <c r="A257" s="2">
         <v>35352</v>
       </c>
-      <c r="B257" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35352</v>
+      <c r="B257" t="s">
+        <v>813</v>
       </c>
       <c r="C257" t="s">
         <v>271</v>
@@ -11373,9 +12771,8 @@
       <c r="A258" s="2">
         <v>35353</v>
       </c>
-      <c r="B258" t="str">
-        <f t="shared" si="3"/>
-        <v>Prchile-35353</v>
+      <c r="B258" s="4" t="s">
+        <v>814</v>
       </c>
       <c r="C258" t="s">
         <v>272</v>
@@ -11409,9 +12806,8 @@
       <c r="A259" s="2">
         <v>35354</v>
       </c>
-      <c r="B259" t="str">
-        <f t="shared" ref="B259:B322" si="4">$B$1&amp;"-"&amp;A259</f>
-        <v>Prchile-35354</v>
+      <c r="B259" t="s">
+        <v>815</v>
       </c>
       <c r="C259" t="s">
         <v>273</v>
@@ -11445,9 +12841,8 @@
       <c r="A260" s="2">
         <v>35355</v>
       </c>
-      <c r="B260" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35355</v>
+      <c r="B260" s="4" t="s">
+        <v>816</v>
       </c>
       <c r="C260" t="s">
         <v>274</v>
@@ -11481,9 +12876,8 @@
       <c r="A261" s="2">
         <v>35356</v>
       </c>
-      <c r="B261" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35356</v>
+      <c r="B261" t="s">
+        <v>817</v>
       </c>
       <c r="C261" t="s">
         <v>275</v>
@@ -11517,9 +12911,8 @@
       <c r="A262" s="2">
         <v>35357</v>
       </c>
-      <c r="B262" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35357</v>
+      <c r="B262" s="4" t="s">
+        <v>818</v>
       </c>
       <c r="C262" t="s">
         <v>276</v>
@@ -11553,9 +12946,8 @@
       <c r="A263" s="2">
         <v>35358</v>
       </c>
-      <c r="B263" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35358</v>
+      <c r="B263" t="s">
+        <v>819</v>
       </c>
       <c r="C263" t="s">
         <v>277</v>
@@ -11589,9 +12981,8 @@
       <c r="A264" s="2">
         <v>35359</v>
       </c>
-      <c r="B264" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35359</v>
+      <c r="B264" s="4" t="s">
+        <v>820</v>
       </c>
       <c r="C264" t="s">
         <v>278</v>
@@ -11625,9 +13016,8 @@
       <c r="A265" s="2">
         <v>35360</v>
       </c>
-      <c r="B265" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35360</v>
+      <c r="B265" t="s">
+        <v>821</v>
       </c>
       <c r="C265" t="s">
         <v>279</v>
@@ -11661,9 +13051,8 @@
       <c r="A266" s="2">
         <v>35361</v>
       </c>
-      <c r="B266" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35361</v>
+      <c r="B266" s="4" t="s">
+        <v>822</v>
       </c>
       <c r="C266" t="s">
         <v>280</v>
@@ -11697,9 +13086,8 @@
       <c r="A267" s="2">
         <v>35362</v>
       </c>
-      <c r="B267" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35362</v>
+      <c r="B267" t="s">
+        <v>823</v>
       </c>
       <c r="C267" t="s">
         <v>281</v>
@@ -11733,9 +13121,8 @@
       <c r="A268" s="2">
         <v>35363</v>
       </c>
-      <c r="B268" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35363</v>
+      <c r="B268" s="4" t="s">
+        <v>824</v>
       </c>
       <c r="C268" t="s">
         <v>282</v>
@@ -11769,9 +13156,8 @@
       <c r="A269" s="2">
         <v>35364</v>
       </c>
-      <c r="B269" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35364</v>
+      <c r="B269" t="s">
+        <v>825</v>
       </c>
       <c r="C269" t="s">
         <v>283</v>
@@ -11805,9 +13191,8 @@
       <c r="A270" s="2">
         <v>35365</v>
       </c>
-      <c r="B270" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35365</v>
+      <c r="B270" s="4" t="s">
+        <v>826</v>
       </c>
       <c r="C270" t="s">
         <v>284</v>
@@ -11841,9 +13226,8 @@
       <c r="A271" s="2">
         <v>35366</v>
       </c>
-      <c r="B271" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35366</v>
+      <c r="B271" t="s">
+        <v>827</v>
       </c>
       <c r="C271" t="s">
         <v>285</v>
@@ -11877,9 +13261,8 @@
       <c r="A272" s="2">
         <v>35367</v>
       </c>
-      <c r="B272" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35367</v>
+      <c r="B272" s="4" t="s">
+        <v>828</v>
       </c>
       <c r="C272" t="s">
         <v>286</v>
@@ -11913,9 +13296,8 @@
       <c r="A273" s="2">
         <v>35368</v>
       </c>
-      <c r="B273" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35368</v>
+      <c r="B273" t="s">
+        <v>829</v>
       </c>
       <c r="C273" t="s">
         <v>287</v>
@@ -11949,9 +13331,8 @@
       <c r="A274" s="2">
         <v>35369</v>
       </c>
-      <c r="B274" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35369</v>
+      <c r="B274" s="4" t="s">
+        <v>830</v>
       </c>
       <c r="C274" t="s">
         <v>288</v>
@@ -11985,9 +13366,8 @@
       <c r="A275" s="2">
         <v>35370</v>
       </c>
-      <c r="B275" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35370</v>
+      <c r="B275" t="s">
+        <v>831</v>
       </c>
       <c r="C275" t="s">
         <v>289</v>
@@ -12021,9 +13401,8 @@
       <c r="A276" s="2">
         <v>35371</v>
       </c>
-      <c r="B276" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35371</v>
+      <c r="B276" s="4" t="s">
+        <v>832</v>
       </c>
       <c r="C276" t="s">
         <v>290</v>
@@ -12057,9 +13436,8 @@
       <c r="A277" s="2">
         <v>35372</v>
       </c>
-      <c r="B277" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35372</v>
+      <c r="B277" t="s">
+        <v>833</v>
       </c>
       <c r="C277" t="s">
         <v>291</v>
@@ -12093,9 +13471,8 @@
       <c r="A278" s="2">
         <v>35373</v>
       </c>
-      <c r="B278" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35373</v>
+      <c r="B278" s="4" t="s">
+        <v>834</v>
       </c>
       <c r="C278" t="s">
         <v>292</v>
@@ -12129,9 +13506,8 @@
       <c r="A279" s="2">
         <v>35374</v>
       </c>
-      <c r="B279" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35374</v>
+      <c r="B279" t="s">
+        <v>835</v>
       </c>
       <c r="C279" t="s">
         <v>293</v>
@@ -12165,9 +13541,8 @@
       <c r="A280" s="2">
         <v>35375</v>
       </c>
-      <c r="B280" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35375</v>
+      <c r="B280" s="4" t="s">
+        <v>836</v>
       </c>
       <c r="C280" t="s">
         <v>294</v>
@@ -12201,9 +13576,8 @@
       <c r="A281" s="2">
         <v>35376</v>
       </c>
-      <c r="B281" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35376</v>
+      <c r="B281" t="s">
+        <v>837</v>
       </c>
       <c r="C281" t="s">
         <v>295</v>
@@ -12237,9 +13611,8 @@
       <c r="A282" s="2">
         <v>35377</v>
       </c>
-      <c r="B282" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35377</v>
+      <c r="B282" s="4" t="s">
+        <v>838</v>
       </c>
       <c r="C282" t="s">
         <v>296</v>
@@ -12273,9 +13646,8 @@
       <c r="A283" s="2">
         <v>35378</v>
       </c>
-      <c r="B283" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35378</v>
+      <c r="B283" t="s">
+        <v>839</v>
       </c>
       <c r="C283" t="s">
         <v>297</v>
@@ -12309,9 +13681,8 @@
       <c r="A284" s="2">
         <v>35379</v>
       </c>
-      <c r="B284" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35379</v>
+      <c r="B284" s="4" t="s">
+        <v>840</v>
       </c>
       <c r="C284" t="s">
         <v>298</v>
@@ -12345,9 +13716,8 @@
       <c r="A285" s="2">
         <v>35380</v>
       </c>
-      <c r="B285" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35380</v>
+      <c r="B285" t="s">
+        <v>841</v>
       </c>
       <c r="C285" t="s">
         <v>299</v>
@@ -12381,9 +13751,8 @@
       <c r="A286" s="2">
         <v>35381</v>
       </c>
-      <c r="B286" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35381</v>
+      <c r="B286" s="4" t="s">
+        <v>842</v>
       </c>
       <c r="C286" t="s">
         <v>300</v>
@@ -12417,9 +13786,8 @@
       <c r="A287" s="2">
         <v>35382</v>
       </c>
-      <c r="B287" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35382</v>
+      <c r="B287" t="s">
+        <v>843</v>
       </c>
       <c r="C287" t="s">
         <v>301</v>
@@ -12453,9 +13821,8 @@
       <c r="A288" s="2">
         <v>35383</v>
       </c>
-      <c r="B288" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35383</v>
+      <c r="B288" s="4" t="s">
+        <v>844</v>
       </c>
       <c r="C288" t="s">
         <v>302</v>
@@ -12489,9 +13856,8 @@
       <c r="A289" s="2">
         <v>35384</v>
       </c>
-      <c r="B289" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35384</v>
+      <c r="B289" t="s">
+        <v>845</v>
       </c>
       <c r="C289" t="s">
         <v>303</v>
@@ -12525,9 +13891,8 @@
       <c r="A290" s="2">
         <v>35385</v>
       </c>
-      <c r="B290" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35385</v>
+      <c r="B290" s="4" t="s">
+        <v>846</v>
       </c>
       <c r="C290" t="s">
         <v>304</v>
@@ -12561,9 +13926,8 @@
       <c r="A291" s="2">
         <v>35386</v>
       </c>
-      <c r="B291" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35386</v>
+      <c r="B291" t="s">
+        <v>847</v>
       </c>
       <c r="C291" t="s">
         <v>305</v>
@@ -12597,9 +13961,8 @@
       <c r="A292" s="2">
         <v>35387</v>
       </c>
-      <c r="B292" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35387</v>
+      <c r="B292" s="4" t="s">
+        <v>848</v>
       </c>
       <c r="C292" t="s">
         <v>306</v>
@@ -12633,9 +13996,8 @@
       <c r="A293" s="2">
         <v>35388</v>
       </c>
-      <c r="B293" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35388</v>
+      <c r="B293" t="s">
+        <v>849</v>
       </c>
       <c r="C293" t="s">
         <v>307</v>
@@ -12669,9 +14031,8 @@
       <c r="A294" s="2">
         <v>35389</v>
       </c>
-      <c r="B294" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35389</v>
+      <c r="B294" s="4" t="s">
+        <v>850</v>
       </c>
       <c r="C294" t="s">
         <v>308</v>
@@ -12705,9 +14066,8 @@
       <c r="A295" s="2">
         <v>35390</v>
       </c>
-      <c r="B295" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35390</v>
+      <c r="B295" t="s">
+        <v>851</v>
       </c>
       <c r="C295" t="s">
         <v>238</v>
@@ -12741,9 +14101,8 @@
       <c r="A296" s="2">
         <v>35391</v>
       </c>
-      <c r="B296" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35391</v>
+      <c r="B296" s="4" t="s">
+        <v>852</v>
       </c>
       <c r="C296" t="s">
         <v>309</v>
@@ -12777,9 +14136,8 @@
       <c r="A297" s="2">
         <v>35392</v>
       </c>
-      <c r="B297" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35392</v>
+      <c r="B297" t="s">
+        <v>853</v>
       </c>
       <c r="C297" t="s">
         <v>310</v>
@@ -12813,9 +14171,8 @@
       <c r="A298" s="2">
         <v>35393</v>
       </c>
-      <c r="B298" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35393</v>
+      <c r="B298" s="4" t="s">
+        <v>854</v>
       </c>
       <c r="C298" t="s">
         <v>311</v>
@@ -12849,9 +14206,8 @@
       <c r="A299" s="2">
         <v>35394</v>
       </c>
-      <c r="B299" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35394</v>
+      <c r="B299" t="s">
+        <v>855</v>
       </c>
       <c r="C299" t="s">
         <v>312</v>
@@ -12885,9 +14241,8 @@
       <c r="A300" s="2">
         <v>35395</v>
       </c>
-      <c r="B300" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35395</v>
+      <c r="B300" s="4" t="s">
+        <v>856</v>
       </c>
       <c r="C300" t="s">
         <v>313</v>
@@ -12921,9 +14276,8 @@
       <c r="A301" s="2">
         <v>35396</v>
       </c>
-      <c r="B301" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35396</v>
+      <c r="B301" t="s">
+        <v>857</v>
       </c>
       <c r="C301" t="s">
         <v>314</v>
@@ -12957,9 +14311,8 @@
       <c r="A302" s="2">
         <v>35397</v>
       </c>
-      <c r="B302" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35397</v>
+      <c r="B302" s="4" t="s">
+        <v>858</v>
       </c>
       <c r="C302" t="s">
         <v>315</v>
@@ -12993,9 +14346,8 @@
       <c r="A303" s="2">
         <v>35398</v>
       </c>
-      <c r="B303" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35398</v>
+      <c r="B303" t="s">
+        <v>859</v>
       </c>
       <c r="C303" t="s">
         <v>316</v>
@@ -13029,9 +14381,8 @@
       <c r="A304" s="2">
         <v>35399</v>
       </c>
-      <c r="B304" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35399</v>
+      <c r="B304" s="4" t="s">
+        <v>860</v>
       </c>
       <c r="C304" t="s">
         <v>317</v>
@@ -13065,9 +14416,8 @@
       <c r="A305" s="2">
         <v>35400</v>
       </c>
-      <c r="B305" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35400</v>
+      <c r="B305" t="s">
+        <v>861</v>
       </c>
       <c r="C305" t="s">
         <v>318</v>
@@ -13101,9 +14451,8 @@
       <c r="A306" s="2">
         <v>35401</v>
       </c>
-      <c r="B306" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35401</v>
+      <c r="B306" s="4" t="s">
+        <v>862</v>
       </c>
       <c r="C306" t="s">
         <v>319</v>
@@ -13137,9 +14486,8 @@
       <c r="A307" s="2">
         <v>35402</v>
       </c>
-      <c r="B307" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35402</v>
+      <c r="B307" t="s">
+        <v>863</v>
       </c>
       <c r="C307" t="s">
         <v>320</v>
@@ -13173,9 +14521,8 @@
       <c r="A308" s="2">
         <v>35403</v>
       </c>
-      <c r="B308" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35403</v>
+      <c r="B308" s="4" t="s">
+        <v>864</v>
       </c>
       <c r="C308" t="s">
         <v>321</v>
@@ -13209,9 +14556,8 @@
       <c r="A309" s="2">
         <v>35404</v>
       </c>
-      <c r="B309" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35404</v>
+      <c r="B309" t="s">
+        <v>865</v>
       </c>
       <c r="C309" t="s">
         <v>322</v>
@@ -13245,9 +14591,8 @@
       <c r="A310" s="2">
         <v>35405</v>
       </c>
-      <c r="B310" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35405</v>
+      <c r="B310" s="4" t="s">
+        <v>866</v>
       </c>
       <c r="C310" t="s">
         <v>323</v>
@@ -13281,9 +14626,8 @@
       <c r="A311" s="2">
         <v>35406</v>
       </c>
-      <c r="B311" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35406</v>
+      <c r="B311" t="s">
+        <v>867</v>
       </c>
       <c r="C311" t="s">
         <v>324</v>
@@ -13317,9 +14661,8 @@
       <c r="A312" s="2">
         <v>35407</v>
       </c>
-      <c r="B312" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35407</v>
+      <c r="B312" s="4" t="s">
+        <v>868</v>
       </c>
       <c r="C312" t="s">
         <v>325</v>
@@ -13353,9 +14696,8 @@
       <c r="A313" s="2">
         <v>35408</v>
       </c>
-      <c r="B313" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35408</v>
+      <c r="B313" t="s">
+        <v>869</v>
       </c>
       <c r="C313" t="s">
         <v>326</v>
@@ -13389,9 +14731,8 @@
       <c r="A314" s="2">
         <v>35409</v>
       </c>
-      <c r="B314" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35409</v>
+      <c r="B314" s="4" t="s">
+        <v>870</v>
       </c>
       <c r="C314" t="s">
         <v>327</v>
@@ -13425,9 +14766,8 @@
       <c r="A315" s="2">
         <v>35410</v>
       </c>
-      <c r="B315" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35410</v>
+      <c r="B315" t="s">
+        <v>871</v>
       </c>
       <c r="C315" t="s">
         <v>328</v>
@@ -13461,9 +14801,8 @@
       <c r="A316" s="2">
         <v>35411</v>
       </c>
-      <c r="B316" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35411</v>
+      <c r="B316" s="4" t="s">
+        <v>872</v>
       </c>
       <c r="C316" t="s">
         <v>329</v>
@@ -13497,9 +14836,8 @@
       <c r="A317" s="2">
         <v>35412</v>
       </c>
-      <c r="B317" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35412</v>
+      <c r="B317" t="s">
+        <v>873</v>
       </c>
       <c r="C317" t="s">
         <v>330</v>
@@ -13533,9 +14871,8 @@
       <c r="A318" s="2">
         <v>35413</v>
       </c>
-      <c r="B318" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35413</v>
+      <c r="B318" s="4" t="s">
+        <v>874</v>
       </c>
       <c r="C318" t="s">
         <v>331</v>
@@ -13569,9 +14906,8 @@
       <c r="A319" s="2">
         <v>35414</v>
       </c>
-      <c r="B319" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35414</v>
+      <c r="B319" t="s">
+        <v>875</v>
       </c>
       <c r="C319" t="s">
         <v>332</v>
@@ -13605,9 +14941,8 @@
       <c r="A320" s="2">
         <v>35415</v>
       </c>
-      <c r="B320" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35415</v>
+      <c r="B320" s="4" t="s">
+        <v>876</v>
       </c>
       <c r="C320" t="s">
         <v>333</v>
@@ -13641,9 +14976,8 @@
       <c r="A321" s="2">
         <v>35416</v>
       </c>
-      <c r="B321" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35416</v>
+      <c r="B321" t="s">
+        <v>877</v>
       </c>
       <c r="C321" t="s">
         <v>334</v>
@@ -13677,9 +15011,8 @@
       <c r="A322" s="2">
         <v>35417</v>
       </c>
-      <c r="B322" t="str">
-        <f t="shared" si="4"/>
-        <v>Prchile-35417</v>
+      <c r="B322" s="4" t="s">
+        <v>878</v>
       </c>
       <c r="C322" t="s">
         <v>335</v>
@@ -13713,9 +15046,8 @@
       <c r="A323" s="2">
         <v>35418</v>
       </c>
-      <c r="B323" t="str">
-        <f t="shared" ref="B323:B386" si="5">$B$1&amp;"-"&amp;A323</f>
-        <v>Prchile-35418</v>
+      <c r="B323" t="s">
+        <v>879</v>
       </c>
       <c r="C323" t="s">
         <v>305</v>
@@ -13749,9 +15081,8 @@
       <c r="A324" s="2">
         <v>35419</v>
       </c>
-      <c r="B324" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35419</v>
+      <c r="B324" s="4" t="s">
+        <v>880</v>
       </c>
       <c r="C324" t="s">
         <v>336</v>
@@ -13785,9 +15116,8 @@
       <c r="A325" s="2">
         <v>35420</v>
       </c>
-      <c r="B325" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35420</v>
+      <c r="B325" t="s">
+        <v>881</v>
       </c>
       <c r="C325" t="s">
         <v>337</v>
@@ -13821,9 +15151,8 @@
       <c r="A326" s="2">
         <v>35421</v>
       </c>
-      <c r="B326" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35421</v>
+      <c r="B326" s="4" t="s">
+        <v>882</v>
       </c>
       <c r="C326" t="s">
         <v>338</v>
@@ -13857,9 +15186,8 @@
       <c r="A327" s="2">
         <v>35422</v>
       </c>
-      <c r="B327" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35422</v>
+      <c r="B327" t="s">
+        <v>883</v>
       </c>
       <c r="C327" t="s">
         <v>339</v>
@@ -13893,9 +15221,8 @@
       <c r="A328" s="2">
         <v>35423</v>
       </c>
-      <c r="B328" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35423</v>
+      <c r="B328" s="4" t="s">
+        <v>884</v>
       </c>
       <c r="C328" t="s">
         <v>340</v>
@@ -13929,9 +15256,8 @@
       <c r="A329" s="2">
         <v>35424</v>
       </c>
-      <c r="B329" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35424</v>
+      <c r="B329" t="s">
+        <v>885</v>
       </c>
       <c r="C329" t="s">
         <v>341</v>
@@ -13965,9 +15291,8 @@
       <c r="A330" s="2">
         <v>35425</v>
       </c>
-      <c r="B330" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35425</v>
+      <c r="B330" s="4" t="s">
+        <v>886</v>
       </c>
       <c r="C330" t="s">
         <v>342</v>
@@ -14001,9 +15326,8 @@
       <c r="A331" s="2">
         <v>35426</v>
       </c>
-      <c r="B331" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35426</v>
+      <c r="B331" t="s">
+        <v>887</v>
       </c>
       <c r="C331" t="s">
         <v>343</v>
@@ -14037,9 +15361,8 @@
       <c r="A332" s="2">
         <v>35427</v>
       </c>
-      <c r="B332" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35427</v>
+      <c r="B332" s="4" t="s">
+        <v>888</v>
       </c>
       <c r="C332" t="s">
         <v>344</v>
@@ -14073,9 +15396,8 @@
       <c r="A333" s="2">
         <v>35428</v>
       </c>
-      <c r="B333" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35428</v>
+      <c r="B333" t="s">
+        <v>889</v>
       </c>
       <c r="C333" t="s">
         <v>345</v>
@@ -14109,9 +15431,8 @@
       <c r="A334" s="2">
         <v>35429</v>
       </c>
-      <c r="B334" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35429</v>
+      <c r="B334" s="4" t="s">
+        <v>890</v>
       </c>
       <c r="C334" t="s">
         <v>346</v>
@@ -14145,9 +15466,8 @@
       <c r="A335" s="2">
         <v>35430</v>
       </c>
-      <c r="B335" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35430</v>
+      <c r="B335" t="s">
+        <v>891</v>
       </c>
       <c r="C335" t="s">
         <v>347</v>
@@ -14181,9 +15501,8 @@
       <c r="A336" s="2">
         <v>35431</v>
       </c>
-      <c r="B336" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35431</v>
+      <c r="B336" s="4" t="s">
+        <v>892</v>
       </c>
       <c r="C336" t="s">
         <v>348</v>
@@ -14217,9 +15536,8 @@
       <c r="A337" s="2">
         <v>35432</v>
       </c>
-      <c r="B337" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35432</v>
+      <c r="B337" t="s">
+        <v>893</v>
       </c>
       <c r="C337" t="s">
         <v>349</v>
@@ -14253,9 +15571,8 @@
       <c r="A338" s="2">
         <v>35433</v>
       </c>
-      <c r="B338" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35433</v>
+      <c r="B338" s="4" t="s">
+        <v>894</v>
       </c>
       <c r="C338" t="s">
         <v>350</v>
@@ -14289,9 +15606,8 @@
       <c r="A339" s="2">
         <v>35434</v>
       </c>
-      <c r="B339" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35434</v>
+      <c r="B339" t="s">
+        <v>895</v>
       </c>
       <c r="C339" t="s">
         <v>351</v>
@@ -14325,9 +15641,8 @@
       <c r="A340" s="2">
         <v>35435</v>
       </c>
-      <c r="B340" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35435</v>
+      <c r="B340" s="4" t="s">
+        <v>896</v>
       </c>
       <c r="C340" t="s">
         <v>352</v>
@@ -14361,9 +15676,8 @@
       <c r="A341" s="2">
         <v>35436</v>
       </c>
-      <c r="B341" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35436</v>
+      <c r="B341" t="s">
+        <v>897</v>
       </c>
       <c r="C341" t="s">
         <v>353</v>
@@ -14397,9 +15711,8 @@
       <c r="A342" s="2">
         <v>35437</v>
       </c>
-      <c r="B342" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35437</v>
+      <c r="B342" s="4" t="s">
+        <v>898</v>
       </c>
       <c r="C342" t="s">
         <v>354</v>
@@ -14433,9 +15746,8 @@
       <c r="A343" s="2">
         <v>35438</v>
       </c>
-      <c r="B343" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35438</v>
+      <c r="B343" t="s">
+        <v>899</v>
       </c>
       <c r="C343" t="s">
         <v>355</v>
@@ -14469,9 +15781,8 @@
       <c r="A344" s="2">
         <v>35439</v>
       </c>
-      <c r="B344" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35439</v>
+      <c r="B344" s="4" t="s">
+        <v>900</v>
       </c>
       <c r="C344" t="s">
         <v>356</v>
@@ -14505,9 +15816,8 @@
       <c r="A345" s="2">
         <v>35440</v>
       </c>
-      <c r="B345" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35440</v>
+      <c r="B345" t="s">
+        <v>901</v>
       </c>
       <c r="C345" t="s">
         <v>357</v>
@@ -14541,9 +15851,8 @@
       <c r="A346" s="2">
         <v>35441</v>
       </c>
-      <c r="B346" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35441</v>
+      <c r="B346" s="4" t="s">
+        <v>902</v>
       </c>
       <c r="C346" t="s">
         <v>358</v>
@@ -14577,9 +15886,8 @@
       <c r="A347" s="2">
         <v>35442</v>
       </c>
-      <c r="B347" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35442</v>
+      <c r="B347" t="s">
+        <v>903</v>
       </c>
       <c r="C347" t="s">
         <v>359</v>
@@ -14613,9 +15921,8 @@
       <c r="A348" s="2">
         <v>35443</v>
       </c>
-      <c r="B348" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35443</v>
+      <c r="B348" s="4" t="s">
+        <v>904</v>
       </c>
       <c r="C348" t="s">
         <v>360</v>
@@ -14649,9 +15956,8 @@
       <c r="A349" s="2">
         <v>35444</v>
       </c>
-      <c r="B349" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35444</v>
+      <c r="B349" t="s">
+        <v>905</v>
       </c>
       <c r="C349" t="s">
         <v>361</v>
@@ -14685,9 +15991,8 @@
       <c r="A350" s="2">
         <v>35445</v>
       </c>
-      <c r="B350" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35445</v>
+      <c r="B350" s="4" t="s">
+        <v>906</v>
       </c>
       <c r="C350" t="s">
         <v>362</v>
@@ -14721,9 +16026,8 @@
       <c r="A351" s="2">
         <v>35446</v>
       </c>
-      <c r="B351" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35446</v>
+      <c r="B351" t="s">
+        <v>907</v>
       </c>
       <c r="C351" t="s">
         <v>363</v>
@@ -14757,9 +16061,8 @@
       <c r="A352" s="2">
         <v>35447</v>
       </c>
-      <c r="B352" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35447</v>
+      <c r="B352" s="4" t="s">
+        <v>908</v>
       </c>
       <c r="C352" t="s">
         <v>364</v>
@@ -14793,9 +16096,8 @@
       <c r="A353" s="2">
         <v>35448</v>
       </c>
-      <c r="B353" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35448</v>
+      <c r="B353" t="s">
+        <v>909</v>
       </c>
       <c r="C353" t="s">
         <v>365</v>
@@ -14829,9 +16131,8 @@
       <c r="A354" s="2">
         <v>35449</v>
       </c>
-      <c r="B354" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35449</v>
+      <c r="B354" s="4" t="s">
+        <v>910</v>
       </c>
       <c r="C354" t="s">
         <v>366</v>
@@ -14865,9 +16166,8 @@
       <c r="A355" s="2">
         <v>35450</v>
       </c>
-      <c r="B355" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35450</v>
+      <c r="B355" t="s">
+        <v>911</v>
       </c>
       <c r="C355" t="s">
         <v>367</v>
@@ -14901,9 +16201,8 @@
       <c r="A356" s="2">
         <v>35451</v>
       </c>
-      <c r="B356" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35451</v>
+      <c r="B356" s="4" t="s">
+        <v>912</v>
       </c>
       <c r="C356" t="s">
         <v>368</v>
@@ -14937,9 +16236,8 @@
       <c r="A357" s="2">
         <v>35452</v>
       </c>
-      <c r="B357" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35452</v>
+      <c r="B357" t="s">
+        <v>913</v>
       </c>
       <c r="C357" t="s">
         <v>369</v>
@@ -14973,9 +16271,8 @@
       <c r="A358" s="2">
         <v>35453</v>
       </c>
-      <c r="B358" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35453</v>
+      <c r="B358" s="4" t="s">
+        <v>914</v>
       </c>
       <c r="C358" t="s">
         <v>370</v>
@@ -15009,9 +16306,8 @@
       <c r="A359" s="2">
         <v>35454</v>
       </c>
-      <c r="B359" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35454</v>
+      <c r="B359" t="s">
+        <v>915</v>
       </c>
       <c r="C359" t="s">
         <v>371</v>
@@ -15045,9 +16341,8 @@
       <c r="A360" s="2">
         <v>35455</v>
       </c>
-      <c r="B360" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35455</v>
+      <c r="B360" s="4" t="s">
+        <v>916</v>
       </c>
       <c r="C360" t="s">
         <v>372</v>
@@ -15081,9 +16376,8 @@
       <c r="A361" s="2">
         <v>35456</v>
       </c>
-      <c r="B361" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35456</v>
+      <c r="B361" t="s">
+        <v>917</v>
       </c>
       <c r="C361" t="s">
         <v>373</v>
@@ -15117,9 +16411,8 @@
       <c r="A362" s="2">
         <v>35457</v>
       </c>
-      <c r="B362" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35457</v>
+      <c r="B362" s="4" t="s">
+        <v>918</v>
       </c>
       <c r="C362" t="s">
         <v>374</v>
@@ -15153,9 +16446,8 @@
       <c r="A363" s="2">
         <v>35458</v>
       </c>
-      <c r="B363" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35458</v>
+      <c r="B363" t="s">
+        <v>919</v>
       </c>
       <c r="C363" t="s">
         <v>375</v>
@@ -15189,9 +16481,8 @@
       <c r="A364" s="2">
         <v>35459</v>
       </c>
-      <c r="B364" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35459</v>
+      <c r="B364" s="4" t="s">
+        <v>920</v>
       </c>
       <c r="C364" t="s">
         <v>376</v>
@@ -15225,9 +16516,8 @@
       <c r="A365" s="2">
         <v>35460</v>
       </c>
-      <c r="B365" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35460</v>
+      <c r="B365" t="s">
+        <v>921</v>
       </c>
       <c r="C365" t="s">
         <v>377</v>
@@ -15261,9 +16551,8 @@
       <c r="A366" s="2">
         <v>35461</v>
       </c>
-      <c r="B366" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35461</v>
+      <c r="B366" s="4" t="s">
+        <v>922</v>
       </c>
       <c r="C366" t="s">
         <v>378</v>
@@ -15297,9 +16586,8 @@
       <c r="A367" s="2">
         <v>35462</v>
       </c>
-      <c r="B367" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35462</v>
+      <c r="B367" t="s">
+        <v>923</v>
       </c>
       <c r="C367" t="s">
         <v>379</v>
@@ -15333,9 +16621,8 @@
       <c r="A368" s="2">
         <v>35463</v>
       </c>
-      <c r="B368" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35463</v>
+      <c r="B368" s="4" t="s">
+        <v>924</v>
       </c>
       <c r="C368" t="s">
         <v>380</v>
@@ -15369,9 +16656,8 @@
       <c r="A369" s="2">
         <v>35464</v>
       </c>
-      <c r="B369" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35464</v>
+      <c r="B369" t="s">
+        <v>925</v>
       </c>
       <c r="C369" t="s">
         <v>381</v>
@@ -15405,9 +16691,8 @@
       <c r="A370" s="2">
         <v>35465</v>
       </c>
-      <c r="B370" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35465</v>
+      <c r="B370" s="4" t="s">
+        <v>926</v>
       </c>
       <c r="C370" t="s">
         <v>382</v>
@@ -15441,9 +16726,8 @@
       <c r="A371" s="2">
         <v>35466</v>
       </c>
-      <c r="B371" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35466</v>
+      <c r="B371" t="s">
+        <v>927</v>
       </c>
       <c r="C371" t="s">
         <v>383</v>
@@ -15477,9 +16761,8 @@
       <c r="A372" s="2">
         <v>35467</v>
       </c>
-      <c r="B372" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35467</v>
+      <c r="B372" s="4" t="s">
+        <v>928</v>
       </c>
       <c r="C372" t="s">
         <v>384</v>
@@ -15513,9 +16796,8 @@
       <c r="A373" s="2">
         <v>35468</v>
       </c>
-      <c r="B373" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35468</v>
+      <c r="B373" t="s">
+        <v>929</v>
       </c>
       <c r="C373" t="s">
         <v>385</v>
@@ -15549,9 +16831,8 @@
       <c r="A374" s="2">
         <v>35469</v>
       </c>
-      <c r="B374" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35469</v>
+      <c r="B374" s="4" t="s">
+        <v>930</v>
       </c>
       <c r="C374" t="s">
         <v>386</v>
@@ -15585,9 +16866,8 @@
       <c r="A375" s="2">
         <v>35470</v>
       </c>
-      <c r="B375" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35470</v>
+      <c r="B375" t="s">
+        <v>931</v>
       </c>
       <c r="C375" t="s">
         <v>387</v>
@@ -15621,9 +16901,8 @@
       <c r="A376" s="2">
         <v>35471</v>
       </c>
-      <c r="B376" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35471</v>
+      <c r="B376" s="4" t="s">
+        <v>932</v>
       </c>
       <c r="C376" t="s">
         <v>388</v>
@@ -15657,9 +16936,8 @@
       <c r="A377" s="2">
         <v>35472</v>
       </c>
-      <c r="B377" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35472</v>
+      <c r="B377" t="s">
+        <v>933</v>
       </c>
       <c r="C377" t="s">
         <v>389</v>
@@ -15693,9 +16971,8 @@
       <c r="A378" s="2">
         <v>35473</v>
       </c>
-      <c r="B378" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35473</v>
+      <c r="B378" s="4" t="s">
+        <v>934</v>
       </c>
       <c r="C378" t="s">
         <v>390</v>
@@ -15729,9 +17006,8 @@
       <c r="A379" s="2">
         <v>35474</v>
       </c>
-      <c r="B379" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35474</v>
+      <c r="B379" t="s">
+        <v>935</v>
       </c>
       <c r="C379" t="s">
         <v>391</v>
@@ -15765,9 +17041,8 @@
       <c r="A380" s="2">
         <v>35475</v>
       </c>
-      <c r="B380" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35475</v>
+      <c r="B380" s="4" t="s">
+        <v>936</v>
       </c>
       <c r="C380" t="s">
         <v>392</v>
@@ -15801,9 +17076,8 @@
       <c r="A381" s="2">
         <v>35476</v>
       </c>
-      <c r="B381" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35476</v>
+      <c r="B381" t="s">
+        <v>937</v>
       </c>
       <c r="C381" t="s">
         <v>393</v>
@@ -15837,9 +17111,8 @@
       <c r="A382" s="2">
         <v>35477</v>
       </c>
-      <c r="B382" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35477</v>
+      <c r="B382" s="4" t="s">
+        <v>938</v>
       </c>
       <c r="C382" t="s">
         <v>394</v>
@@ -15873,9 +17146,8 @@
       <c r="A383" s="2">
         <v>35478</v>
       </c>
-      <c r="B383" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35478</v>
+      <c r="B383" t="s">
+        <v>939</v>
       </c>
       <c r="C383" t="s">
         <v>395</v>
@@ -15909,9 +17181,8 @@
       <c r="A384" s="2">
         <v>35479</v>
       </c>
-      <c r="B384" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35479</v>
+      <c r="B384" s="4" t="s">
+        <v>940</v>
       </c>
       <c r="C384" t="s">
         <v>396</v>
@@ -15945,9 +17216,8 @@
       <c r="A385" s="2">
         <v>35480</v>
       </c>
-      <c r="B385" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35480</v>
+      <c r="B385" t="s">
+        <v>941</v>
       </c>
       <c r="C385" t="s">
         <v>397</v>
@@ -15981,9 +17251,8 @@
       <c r="A386" s="2">
         <v>35481</v>
       </c>
-      <c r="B386" t="str">
-        <f t="shared" si="5"/>
-        <v>Prchile-35481</v>
+      <c r="B386" s="4" t="s">
+        <v>942</v>
       </c>
       <c r="C386" t="s">
         <v>398</v>
@@ -16017,9 +17286,8 @@
       <c r="A387" s="2">
         <v>35482</v>
       </c>
-      <c r="B387" t="str">
-        <f t="shared" ref="B387:B450" si="6">$B$1&amp;"-"&amp;A387</f>
-        <v>Prchile-35482</v>
+      <c r="B387" t="s">
+        <v>943</v>
       </c>
       <c r="C387" t="s">
         <v>399</v>
@@ -16053,9 +17321,8 @@
       <c r="A388" s="2">
         <v>35483</v>
       </c>
-      <c r="B388" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35483</v>
+      <c r="B388" s="4" t="s">
+        <v>944</v>
       </c>
       <c r="C388" t="s">
         <v>400</v>
@@ -16089,9 +17356,8 @@
       <c r="A389" s="2">
         <v>35484</v>
       </c>
-      <c r="B389" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35484</v>
+      <c r="B389" t="s">
+        <v>945</v>
       </c>
       <c r="C389" t="s">
         <v>401</v>
@@ -16125,9 +17391,8 @@
       <c r="A390" s="2">
         <v>35485</v>
       </c>
-      <c r="B390" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35485</v>
+      <c r="B390" s="4" t="s">
+        <v>946</v>
       </c>
       <c r="C390" t="s">
         <v>402</v>
@@ -16161,9 +17426,8 @@
       <c r="A391" s="2">
         <v>35486</v>
       </c>
-      <c r="B391" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35486</v>
+      <c r="B391" t="s">
+        <v>947</v>
       </c>
       <c r="C391" t="s">
         <v>403</v>
@@ -16197,9 +17461,8 @@
       <c r="A392" s="2">
         <v>35487</v>
       </c>
-      <c r="B392" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35487</v>
+      <c r="B392" s="4" t="s">
+        <v>948</v>
       </c>
       <c r="C392" t="s">
         <v>404</v>
@@ -16233,9 +17496,8 @@
       <c r="A393" s="2">
         <v>35488</v>
       </c>
-      <c r="B393" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35488</v>
+      <c r="B393" t="s">
+        <v>949</v>
       </c>
       <c r="C393" t="s">
         <v>405</v>
@@ -16269,9 +17531,8 @@
       <c r="A394" s="2">
         <v>35489</v>
       </c>
-      <c r="B394" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35489</v>
+      <c r="B394" s="4" t="s">
+        <v>950</v>
       </c>
       <c r="C394" t="s">
         <v>406</v>
@@ -16305,9 +17566,8 @@
       <c r="A395" s="2">
         <v>35490</v>
       </c>
-      <c r="B395" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35490</v>
+      <c r="B395" t="s">
+        <v>951</v>
       </c>
       <c r="C395" t="s">
         <v>407</v>
@@ -16341,9 +17601,8 @@
       <c r="A396" s="2">
         <v>35491</v>
       </c>
-      <c r="B396" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35491</v>
+      <c r="B396" s="4" t="s">
+        <v>952</v>
       </c>
       <c r="C396" t="s">
         <v>408</v>
@@ -16377,9 +17636,8 @@
       <c r="A397" s="2">
         <v>35492</v>
       </c>
-      <c r="B397" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35492</v>
+      <c r="B397" t="s">
+        <v>953</v>
       </c>
       <c r="C397" t="s">
         <v>409</v>
@@ -16413,9 +17671,8 @@
       <c r="A398" s="2">
         <v>35493</v>
       </c>
-      <c r="B398" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35493</v>
+      <c r="B398" s="4" t="s">
+        <v>954</v>
       </c>
       <c r="C398" t="s">
         <v>410</v>
@@ -16449,9 +17706,8 @@
       <c r="A399" s="2">
         <v>35494</v>
       </c>
-      <c r="B399" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35494</v>
+      <c r="B399" t="s">
+        <v>955</v>
       </c>
       <c r="C399" t="s">
         <v>411</v>
@@ -16485,9 +17741,8 @@
       <c r="A400" s="2">
         <v>35495</v>
       </c>
-      <c r="B400" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35495</v>
+      <c r="B400" s="4" t="s">
+        <v>956</v>
       </c>
       <c r="C400" t="s">
         <v>412</v>
@@ -16521,9 +17776,8 @@
       <c r="A401" s="2">
         <v>35496</v>
       </c>
-      <c r="B401" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35496</v>
+      <c r="B401" t="s">
+        <v>957</v>
       </c>
       <c r="C401" t="s">
         <v>413</v>
@@ -16557,9 +17811,8 @@
       <c r="A402" s="2">
         <v>35497</v>
       </c>
-      <c r="B402" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35497</v>
+      <c r="B402" s="4" t="s">
+        <v>958</v>
       </c>
       <c r="C402" t="s">
         <v>414</v>
@@ -16593,9 +17846,8 @@
       <c r="A403" s="2">
         <v>35498</v>
       </c>
-      <c r="B403" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35498</v>
+      <c r="B403" t="s">
+        <v>959</v>
       </c>
       <c r="C403" t="s">
         <v>415</v>
@@ -16629,9 +17881,8 @@
       <c r="A404" s="2">
         <v>35499</v>
       </c>
-      <c r="B404" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35499</v>
+      <c r="B404" s="4" t="s">
+        <v>960</v>
       </c>
       <c r="C404" t="s">
         <v>416</v>
@@ -16665,9 +17916,8 @@
       <c r="A405" s="2">
         <v>35500</v>
       </c>
-      <c r="B405" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35500</v>
+      <c r="B405" t="s">
+        <v>961</v>
       </c>
       <c r="C405" t="s">
         <v>417</v>
@@ -16701,9 +17951,8 @@
       <c r="A406" s="2">
         <v>35501</v>
       </c>
-      <c r="B406" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35501</v>
+      <c r="B406" s="4" t="s">
+        <v>962</v>
       </c>
       <c r="C406" t="s">
         <v>418</v>
@@ -16737,9 +17986,8 @@
       <c r="A407" s="2">
         <v>35502</v>
       </c>
-      <c r="B407" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35502</v>
+      <c r="B407" t="s">
+        <v>963</v>
       </c>
       <c r="C407" t="s">
         <v>419</v>
@@ -16773,9 +18021,8 @@
       <c r="A408" s="2">
         <v>35503</v>
       </c>
-      <c r="B408" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35503</v>
+      <c r="B408" s="4" t="s">
+        <v>964</v>
       </c>
       <c r="C408" t="s">
         <v>420</v>
@@ -16809,9 +18056,8 @@
       <c r="A409" s="2">
         <v>35504</v>
       </c>
-      <c r="B409" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35504</v>
+      <c r="B409" t="s">
+        <v>965</v>
       </c>
       <c r="C409" t="s">
         <v>421</v>
@@ -16845,9 +18091,8 @@
       <c r="A410" s="2">
         <v>35505</v>
       </c>
-      <c r="B410" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35505</v>
+      <c r="B410" s="4" t="s">
+        <v>966</v>
       </c>
       <c r="C410" t="s">
         <v>422</v>
@@ -16881,9 +18126,8 @@
       <c r="A411" s="2">
         <v>35506</v>
       </c>
-      <c r="B411" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35506</v>
+      <c r="B411" t="s">
+        <v>967</v>
       </c>
       <c r="C411" t="s">
         <v>423</v>
@@ -16917,9 +18161,8 @@
       <c r="A412" s="2">
         <v>35507</v>
       </c>
-      <c r="B412" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35507</v>
+      <c r="B412" s="4" t="s">
+        <v>968</v>
       </c>
       <c r="C412" t="s">
         <v>424</v>
@@ -16953,9 +18196,8 @@
       <c r="A413" s="2">
         <v>35508</v>
       </c>
-      <c r="B413" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35508</v>
+      <c r="B413" t="s">
+        <v>969</v>
       </c>
       <c r="C413" t="s">
         <v>425</v>
@@ -16989,9 +18231,8 @@
       <c r="A414" s="2">
         <v>35509</v>
       </c>
-      <c r="B414" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35509</v>
+      <c r="B414" s="4" t="s">
+        <v>970</v>
       </c>
       <c r="C414" t="s">
         <v>426</v>
@@ -17025,9 +18266,8 @@
       <c r="A415" s="2">
         <v>35510</v>
       </c>
-      <c r="B415" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35510</v>
+      <c r="B415" t="s">
+        <v>971</v>
       </c>
       <c r="C415" t="s">
         <v>427</v>
@@ -17061,9 +18301,8 @@
       <c r="A416" s="2">
         <v>35511</v>
       </c>
-      <c r="B416" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35511</v>
+      <c r="B416" s="4" t="s">
+        <v>972</v>
       </c>
       <c r="C416" t="s">
         <v>428</v>
@@ -17097,9 +18336,8 @@
       <c r="A417" s="2">
         <v>35512</v>
       </c>
-      <c r="B417" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35512</v>
+      <c r="B417" t="s">
+        <v>973</v>
       </c>
       <c r="C417" t="s">
         <v>429</v>
@@ -17133,9 +18371,8 @@
       <c r="A418" s="2">
         <v>35513</v>
       </c>
-      <c r="B418" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35513</v>
+      <c r="B418" s="4" t="s">
+        <v>974</v>
       </c>
       <c r="C418" t="s">
         <v>430</v>
@@ -17169,9 +18406,8 @@
       <c r="A419" s="2">
         <v>35514</v>
       </c>
-      <c r="B419" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35514</v>
+      <c r="B419" t="s">
+        <v>975</v>
       </c>
       <c r="C419" t="s">
         <v>431</v>
@@ -17205,9 +18441,8 @@
       <c r="A420" s="2">
         <v>35515</v>
       </c>
-      <c r="B420" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35515</v>
+      <c r="B420" s="4" t="s">
+        <v>976</v>
       </c>
       <c r="C420" t="s">
         <v>432</v>
@@ -17241,9 +18476,8 @@
       <c r="A421" s="2">
         <v>35516</v>
       </c>
-      <c r="B421" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35516</v>
+      <c r="B421" t="s">
+        <v>977</v>
       </c>
       <c r="C421" t="s">
         <v>433</v>
@@ -17277,9 +18511,8 @@
       <c r="A422" s="2">
         <v>35517</v>
       </c>
-      <c r="B422" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35517</v>
+      <c r="B422" s="4" t="s">
+        <v>978</v>
       </c>
       <c r="C422" t="s">
         <v>434</v>
@@ -17313,9 +18546,8 @@
       <c r="A423" s="2">
         <v>35518</v>
       </c>
-      <c r="B423" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35518</v>
+      <c r="B423" t="s">
+        <v>979</v>
       </c>
       <c r="C423" t="s">
         <v>436</v>
@@ -17349,9 +18581,8 @@
       <c r="A424" s="2">
         <v>35519</v>
       </c>
-      <c r="B424" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35519</v>
+      <c r="B424" s="4" t="s">
+        <v>980</v>
       </c>
       <c r="C424" t="s">
         <v>437</v>
@@ -17385,9 +18616,8 @@
       <c r="A425" s="2">
         <v>35520</v>
       </c>
-      <c r="B425" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35520</v>
+      <c r="B425" t="s">
+        <v>981</v>
       </c>
       <c r="C425" t="s">
         <v>438</v>
@@ -17421,9 +18651,8 @@
       <c r="A426" s="2">
         <v>35521</v>
       </c>
-      <c r="B426" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35521</v>
+      <c r="B426" s="4" t="s">
+        <v>982</v>
       </c>
       <c r="C426" t="s">
         <v>439</v>
@@ -17457,9 +18686,8 @@
       <c r="A427" s="2">
         <v>35522</v>
       </c>
-      <c r="B427" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35522</v>
+      <c r="B427" t="s">
+        <v>983</v>
       </c>
       <c r="C427" t="s">
         <v>440</v>
@@ -17493,9 +18721,8 @@
       <c r="A428" s="2">
         <v>35523</v>
       </c>
-      <c r="B428" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35523</v>
+      <c r="B428" s="4" t="s">
+        <v>984</v>
       </c>
       <c r="C428" t="s">
         <v>441</v>
@@ -17529,9 +18756,8 @@
       <c r="A429" s="2">
         <v>35524</v>
       </c>
-      <c r="B429" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35524</v>
+      <c r="B429" t="s">
+        <v>985</v>
       </c>
       <c r="C429" t="s">
         <v>442</v>
@@ -17565,9 +18791,8 @@
       <c r="A430" s="2">
         <v>35525</v>
       </c>
-      <c r="B430" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35525</v>
+      <c r="B430" s="4" t="s">
+        <v>986</v>
       </c>
       <c r="C430" t="s">
         <v>443</v>
@@ -17601,9 +18826,8 @@
       <c r="A431" s="2">
         <v>35526</v>
       </c>
-      <c r="B431" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35526</v>
+      <c r="B431" t="s">
+        <v>987</v>
       </c>
       <c r="C431" t="s">
         <v>444</v>
@@ -17637,9 +18861,8 @@
       <c r="A432" s="2">
         <v>35527</v>
       </c>
-      <c r="B432" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35527</v>
+      <c r="B432" s="4" t="s">
+        <v>988</v>
       </c>
       <c r="C432" t="s">
         <v>445</v>
@@ -17673,9 +18896,8 @@
       <c r="A433" s="2">
         <v>35528</v>
       </c>
-      <c r="B433" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35528</v>
+      <c r="B433" t="s">
+        <v>989</v>
       </c>
       <c r="C433" t="s">
         <v>446</v>
@@ -17709,9 +18931,8 @@
       <c r="A434" s="2">
         <v>35529</v>
       </c>
-      <c r="B434" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35529</v>
+      <c r="B434" s="4" t="s">
+        <v>990</v>
       </c>
       <c r="C434" t="s">
         <v>447</v>
@@ -17745,9 +18966,8 @@
       <c r="A435" s="2">
         <v>35530</v>
       </c>
-      <c r="B435" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35530</v>
+      <c r="B435" t="s">
+        <v>991</v>
       </c>
       <c r="C435" t="s">
         <v>448</v>
@@ -17781,9 +19001,8 @@
       <c r="A436" s="2">
         <v>35531</v>
       </c>
-      <c r="B436" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35531</v>
+      <c r="B436" s="4" t="s">
+        <v>992</v>
       </c>
       <c r="C436" t="s">
         <v>449</v>
@@ -17817,9 +19036,8 @@
       <c r="A437" s="2">
         <v>35532</v>
       </c>
-      <c r="B437" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35532</v>
+      <c r="B437" t="s">
+        <v>993</v>
       </c>
       <c r="C437" t="s">
         <v>450</v>
@@ -17853,9 +19071,8 @@
       <c r="A438" s="2">
         <v>35533</v>
       </c>
-      <c r="B438" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35533</v>
+      <c r="B438" s="4" t="s">
+        <v>994</v>
       </c>
       <c r="C438" t="s">
         <v>451</v>
@@ -17889,9 +19106,8 @@
       <c r="A439" s="2">
         <v>35534</v>
       </c>
-      <c r="B439" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35534</v>
+      <c r="B439" t="s">
+        <v>995</v>
       </c>
       <c r="C439" t="s">
         <v>452</v>
@@ -17925,9 +19141,8 @@
       <c r="A440" s="2">
         <v>35535</v>
       </c>
-      <c r="B440" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35535</v>
+      <c r="B440" s="4" t="s">
+        <v>996</v>
       </c>
       <c r="C440" t="s">
         <v>453</v>
@@ -17961,9 +19176,8 @@
       <c r="A441" s="2">
         <v>35536</v>
       </c>
-      <c r="B441" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35536</v>
+      <c r="B441" t="s">
+        <v>997</v>
       </c>
       <c r="C441" t="s">
         <v>454</v>
@@ -17997,9 +19211,8 @@
       <c r="A442" s="2">
         <v>35537</v>
       </c>
-      <c r="B442" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35537</v>
+      <c r="B442" s="4" t="s">
+        <v>998</v>
       </c>
       <c r="C442" t="s">
         <v>455</v>
@@ -18033,9 +19246,8 @@
       <c r="A443" s="2">
         <v>35538</v>
       </c>
-      <c r="B443" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35538</v>
+      <c r="B443" t="s">
+        <v>999</v>
       </c>
       <c r="C443" t="s">
         <v>456</v>
@@ -18069,9 +19281,8 @@
       <c r="A444" s="2">
         <v>35539</v>
       </c>
-      <c r="B444" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35539</v>
+      <c r="B444" s="4" t="s">
+        <v>1000</v>
       </c>
       <c r="C444" t="s">
         <v>457</v>
@@ -18105,9 +19316,8 @@
       <c r="A445" s="2">
         <v>35540</v>
       </c>
-      <c r="B445" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35540</v>
+      <c r="B445" t="s">
+        <v>1001</v>
       </c>
       <c r="C445" t="s">
         <v>458</v>
@@ -18141,9 +19351,8 @@
       <c r="A446" s="2">
         <v>35541</v>
       </c>
-      <c r="B446" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35541</v>
+      <c r="B446" s="4" t="s">
+        <v>1002</v>
       </c>
       <c r="C446" t="s">
         <v>459</v>
@@ -18177,9 +19386,8 @@
       <c r="A447" s="2">
         <v>35542</v>
       </c>
-      <c r="B447" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35542</v>
+      <c r="B447" t="s">
+        <v>1003</v>
       </c>
       <c r="C447" t="s">
         <v>460</v>
@@ -18213,9 +19421,8 @@
       <c r="A448" s="2">
         <v>35543</v>
       </c>
-      <c r="B448" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35543</v>
+      <c r="B448" s="4" t="s">
+        <v>1004</v>
       </c>
       <c r="C448" t="s">
         <v>461</v>
@@ -18249,9 +19456,8 @@
       <c r="A449" s="2">
         <v>35544</v>
       </c>
-      <c r="B449" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35544</v>
+      <c r="B449" t="s">
+        <v>1005</v>
       </c>
       <c r="C449" t="s">
         <v>462</v>
@@ -18285,9 +19491,8 @@
       <c r="A450" s="2">
         <v>35545</v>
       </c>
-      <c r="B450" t="str">
-        <f t="shared" si="6"/>
-        <v>Prchile-35545</v>
+      <c r="B450" s="4" t="s">
+        <v>1006</v>
       </c>
       <c r="C450" t="s">
         <v>463</v>
@@ -18321,9 +19526,8 @@
       <c r="A451" s="2">
         <v>35546</v>
       </c>
-      <c r="B451" t="str">
-        <f t="shared" ref="B451:B514" si="7">$B$1&amp;"-"&amp;A451</f>
-        <v>Prchile-35546</v>
+      <c r="B451" t="s">
+        <v>1007</v>
       </c>
       <c r="C451" t="s">
         <v>464</v>
@@ -18357,9 +19561,8 @@
       <c r="A452" s="2">
         <v>35547</v>
       </c>
-      <c r="B452" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35547</v>
+      <c r="B452" s="4" t="s">
+        <v>1008</v>
       </c>
       <c r="C452" t="s">
         <v>465</v>
@@ -18393,9 +19596,8 @@
       <c r="A453" s="2">
         <v>35548</v>
       </c>
-      <c r="B453" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35548</v>
+      <c r="B453" t="s">
+        <v>1009</v>
       </c>
       <c r="C453" t="s">
         <v>470</v>
@@ -18429,9 +19631,8 @@
       <c r="A454" s="2">
         <v>35549</v>
       </c>
-      <c r="B454" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35549</v>
+      <c r="B454" s="4" t="s">
+        <v>1010</v>
       </c>
       <c r="C454" t="s">
         <v>471</v>
@@ -18465,9 +19666,8 @@
       <c r="A455" s="2">
         <v>35550</v>
       </c>
-      <c r="B455" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35550</v>
+      <c r="B455" t="s">
+        <v>1011</v>
       </c>
       <c r="C455" t="s">
         <v>472</v>
@@ -18501,9 +19701,8 @@
       <c r="A456" s="2">
         <v>35551</v>
       </c>
-      <c r="B456" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35551</v>
+      <c r="B456" s="4" t="s">
+        <v>1012</v>
       </c>
       <c r="C456" t="s">
         <v>473</v>
@@ -18537,9 +19736,8 @@
       <c r="A457" s="2">
         <v>35552</v>
       </c>
-      <c r="B457" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35552</v>
+      <c r="B457" t="s">
+        <v>1013</v>
       </c>
       <c r="C457" t="s">
         <v>474</v>
@@ -18573,9 +19771,8 @@
       <c r="A458" s="2">
         <v>35553</v>
       </c>
-      <c r="B458" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35553</v>
+      <c r="B458" s="4" t="s">
+        <v>1014</v>
       </c>
       <c r="C458" t="s">
         <v>475</v>
@@ -18609,9 +19806,8 @@
       <c r="A459" s="2">
         <v>35554</v>
       </c>
-      <c r="B459" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35554</v>
+      <c r="B459" t="s">
+        <v>1015</v>
       </c>
       <c r="C459" t="s">
         <v>476</v>
@@ -18645,9 +19841,8 @@
       <c r="A460" s="2">
         <v>35555</v>
       </c>
-      <c r="B460" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35555</v>
+      <c r="B460" s="4" t="s">
+        <v>1016</v>
       </c>
       <c r="C460" t="s">
         <v>477</v>
@@ -18681,9 +19876,8 @@
       <c r="A461" s="2">
         <v>35556</v>
       </c>
-      <c r="B461" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35556</v>
+      <c r="B461" t="s">
+        <v>1017</v>
       </c>
       <c r="C461" t="s">
         <v>478</v>
@@ -18717,9 +19911,8 @@
       <c r="A462" s="2">
         <v>35557</v>
       </c>
-      <c r="B462" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35557</v>
+      <c r="B462" s="4" t="s">
+        <v>1018</v>
       </c>
       <c r="C462" t="s">
         <v>479</v>
@@ -18753,9 +19946,8 @@
       <c r="A463" s="2">
         <v>35558</v>
       </c>
-      <c r="B463" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35558</v>
+      <c r="B463" t="s">
+        <v>1019</v>
       </c>
       <c r="C463" t="s">
         <v>480</v>
@@ -18789,9 +19981,8 @@
       <c r="A464" s="2">
         <v>35559</v>
       </c>
-      <c r="B464" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35559</v>
+      <c r="B464" s="4" t="s">
+        <v>1020</v>
       </c>
       <c r="C464" t="s">
         <v>481</v>
@@ -18825,9 +20016,8 @@
       <c r="A465" s="2">
         <v>35560</v>
       </c>
-      <c r="B465" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35560</v>
+      <c r="B465" t="s">
+        <v>1021</v>
       </c>
       <c r="C465" t="s">
         <v>482</v>
@@ -18861,9 +20051,8 @@
       <c r="A466" s="2">
         <v>35561</v>
       </c>
-      <c r="B466" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35561</v>
+      <c r="B466" s="4" t="s">
+        <v>1022</v>
       </c>
       <c r="C466" t="s">
         <v>483</v>
@@ -18897,9 +20086,8 @@
       <c r="A467" s="2">
         <v>35562</v>
       </c>
-      <c r="B467" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35562</v>
+      <c r="B467" t="s">
+        <v>1023</v>
       </c>
       <c r="C467" t="s">
         <v>484</v>
@@ -18933,9 +20121,8 @@
       <c r="A468" s="2">
         <v>35563</v>
       </c>
-      <c r="B468" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35563</v>
+      <c r="B468" s="4" t="s">
+        <v>1024</v>
       </c>
       <c r="C468" t="s">
         <v>485</v>
@@ -18969,9 +20156,8 @@
       <c r="A469" s="2">
         <v>35564</v>
       </c>
-      <c r="B469" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35564</v>
+      <c r="B469" t="s">
+        <v>1025</v>
       </c>
       <c r="C469" t="s">
         <v>486</v>
@@ -19005,9 +20191,8 @@
       <c r="A470" s="2">
         <v>35565</v>
       </c>
-      <c r="B470" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35565</v>
+      <c r="B470" s="4" t="s">
+        <v>1026</v>
       </c>
       <c r="C470" t="s">
         <v>487</v>
@@ -19041,9 +20226,8 @@
       <c r="A471" s="2">
         <v>35566</v>
       </c>
-      <c r="B471" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35566</v>
+      <c r="B471" t="s">
+        <v>1027</v>
       </c>
       <c r="C471" t="s">
         <v>488</v>
@@ -19077,9 +20261,8 @@
       <c r="A472" s="2">
         <v>35567</v>
       </c>
-      <c r="B472" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35567</v>
+      <c r="B472" s="4" t="s">
+        <v>1028</v>
       </c>
       <c r="C472" t="s">
         <v>489</v>
@@ -19113,9 +20296,8 @@
       <c r="A473" s="2">
         <v>35568</v>
       </c>
-      <c r="B473" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35568</v>
+      <c r="B473" t="s">
+        <v>1029</v>
       </c>
       <c r="C473" t="s">
         <v>490</v>
@@ -19149,9 +20331,8 @@
       <c r="A474" s="2">
         <v>35569</v>
       </c>
-      <c r="B474" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35569</v>
+      <c r="B474" s="4" t="s">
+        <v>1030</v>
       </c>
       <c r="C474" t="s">
         <v>491</v>
@@ -19185,9 +20366,8 @@
       <c r="A475" s="2">
         <v>35570</v>
       </c>
-      <c r="B475" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35570</v>
+      <c r="B475" t="s">
+        <v>1031</v>
       </c>
       <c r="C475" t="s">
         <v>492</v>
@@ -19221,9 +20401,8 @@
       <c r="A476" s="2">
         <v>35571</v>
       </c>
-      <c r="B476" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35571</v>
+      <c r="B476" s="4" t="s">
+        <v>1032</v>
       </c>
       <c r="C476" t="s">
         <v>493</v>
@@ -19257,9 +20436,8 @@
       <c r="A477" s="2">
         <v>35572</v>
       </c>
-      <c r="B477" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35572</v>
+      <c r="B477" t="s">
+        <v>1033</v>
       </c>
       <c r="C477" t="s">
         <v>494</v>
@@ -19293,9 +20471,8 @@
       <c r="A478" s="2">
         <v>35573</v>
       </c>
-      <c r="B478" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35573</v>
+      <c r="B478" s="4" t="s">
+        <v>1034</v>
       </c>
       <c r="C478" t="s">
         <v>495</v>
@@ -19329,9 +20506,8 @@
       <c r="A479" s="2">
         <v>35574</v>
       </c>
-      <c r="B479" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35574</v>
+      <c r="B479" t="s">
+        <v>1035</v>
       </c>
       <c r="C479" t="s">
         <v>496</v>
@@ -19365,9 +20541,8 @@
       <c r="A480" s="2">
         <v>35575</v>
       </c>
-      <c r="B480" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35575</v>
+      <c r="B480" s="4" t="s">
+        <v>1036</v>
       </c>
       <c r="C480" t="s">
         <v>497</v>
@@ -19401,9 +20576,8 @@
       <c r="A481" s="2">
         <v>35576</v>
       </c>
-      <c r="B481" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35576</v>
+      <c r="B481" t="s">
+        <v>1037</v>
       </c>
       <c r="C481" t="s">
         <v>498</v>
@@ -19437,9 +20611,8 @@
       <c r="A482" s="2">
         <v>35577</v>
       </c>
-      <c r="B482" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35577</v>
+      <c r="B482" s="4" t="s">
+        <v>1038</v>
       </c>
       <c r="C482" t="s">
         <v>499</v>
@@ -19473,9 +20646,8 @@
       <c r="A483" s="2">
         <v>35578</v>
       </c>
-      <c r="B483" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35578</v>
+      <c r="B483" t="s">
+        <v>1039</v>
       </c>
       <c r="C483" t="s">
         <v>500</v>
@@ -19509,9 +20681,8 @@
       <c r="A484" s="2">
         <v>35579</v>
       </c>
-      <c r="B484" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35579</v>
+      <c r="B484" s="4" t="s">
+        <v>1040</v>
       </c>
       <c r="C484" t="s">
         <v>501</v>
@@ -19545,9 +20716,8 @@
       <c r="A485" s="2">
         <v>35580</v>
       </c>
-      <c r="B485" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35580</v>
+      <c r="B485" t="s">
+        <v>1041</v>
       </c>
       <c r="C485" t="s">
         <v>502</v>
@@ -19581,9 +20751,8 @@
       <c r="A486" s="2">
         <v>35581</v>
       </c>
-      <c r="B486" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35581</v>
+      <c r="B486" s="4" t="s">
+        <v>1042</v>
       </c>
       <c r="C486" t="s">
         <v>503</v>
@@ -19617,9 +20786,8 @@
       <c r="A487" s="2">
         <v>35582</v>
       </c>
-      <c r="B487" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35582</v>
+      <c r="B487" t="s">
+        <v>1043</v>
       </c>
       <c r="C487" t="s">
         <v>504</v>
@@ -19653,9 +20821,8 @@
       <c r="A488" s="2">
         <v>35583</v>
       </c>
-      <c r="B488" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35583</v>
+      <c r="B488" s="4" t="s">
+        <v>1044</v>
       </c>
       <c r="C488" t="s">
         <v>505</v>
@@ -19689,9 +20856,8 @@
       <c r="A489" s="2">
         <v>35584</v>
       </c>
-      <c r="B489" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35584</v>
+      <c r="B489" t="s">
+        <v>1045</v>
       </c>
       <c r="C489" t="s">
         <v>506</v>
@@ -19725,9 +20891,8 @@
       <c r="A490" s="2">
         <v>35585</v>
       </c>
-      <c r="B490" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35585</v>
+      <c r="B490" s="4" t="s">
+        <v>1046</v>
       </c>
       <c r="C490" t="s">
         <v>507</v>
@@ -19761,9 +20926,8 @@
       <c r="A491" s="2">
         <v>35586</v>
       </c>
-      <c r="B491" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35586</v>
+      <c r="B491" t="s">
+        <v>1047</v>
       </c>
       <c r="C491" t="s">
         <v>508</v>
@@ -19797,9 +20961,8 @@
       <c r="A492" s="2">
         <v>35587</v>
       </c>
-      <c r="B492" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35587</v>
+      <c r="B492" s="4" t="s">
+        <v>1048</v>
       </c>
       <c r="C492" t="s">
         <v>509</v>
@@ -19833,9 +20996,8 @@
       <c r="A493" s="2">
         <v>35588</v>
       </c>
-      <c r="B493" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35588</v>
+      <c r="B493" t="s">
+        <v>1049</v>
       </c>
       <c r="C493" t="s">
         <v>510</v>
@@ -19869,9 +21031,8 @@
       <c r="A494" s="2">
         <v>35589</v>
       </c>
-      <c r="B494" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35589</v>
+      <c r="B494" s="4" t="s">
+        <v>1050</v>
       </c>
       <c r="C494" t="s">
         <v>493</v>
@@ -19905,9 +21066,8 @@
       <c r="A495" s="2">
         <v>35590</v>
       </c>
-      <c r="B495" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35590</v>
+      <c r="B495" t="s">
+        <v>1051</v>
       </c>
       <c r="C495" t="s">
         <v>493</v>
@@ -19941,9 +21101,8 @@
       <c r="A496" s="2">
         <v>35591</v>
       </c>
-      <c r="B496" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35591</v>
+      <c r="B496" s="4" t="s">
+        <v>1052</v>
       </c>
       <c r="C496" t="s">
         <v>493</v>
@@ -19977,9 +21136,8 @@
       <c r="A497" s="2">
         <v>35592</v>
       </c>
-      <c r="B497" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35592</v>
+      <c r="B497" t="s">
+        <v>1053</v>
       </c>
       <c r="C497" t="s">
         <v>511</v>
@@ -20013,9 +21171,8 @@
       <c r="A498" s="2">
         <v>35593</v>
       </c>
-      <c r="B498" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35593</v>
+      <c r="B498" s="4" t="s">
+        <v>1054</v>
       </c>
       <c r="C498" t="s">
         <v>512</v>
@@ -20049,9 +21206,8 @@
       <c r="A499" s="2">
         <v>35594</v>
       </c>
-      <c r="B499" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35594</v>
+      <c r="B499" t="s">
+        <v>1055</v>
       </c>
       <c r="C499" t="s">
         <v>493</v>
@@ -20085,9 +21241,8 @@
       <c r="A500" s="2">
         <v>35595</v>
       </c>
-      <c r="B500" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35595</v>
+      <c r="B500" s="4" t="s">
+        <v>1056</v>
       </c>
       <c r="C500" t="s">
         <v>513</v>
@@ -20121,9 +21276,8 @@
       <c r="A501" s="2">
         <v>35596</v>
       </c>
-      <c r="B501" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35596</v>
+      <c r="B501" t="s">
+        <v>1057</v>
       </c>
       <c r="C501" t="s">
         <v>514</v>
@@ -20157,9 +21311,8 @@
       <c r="A502" s="2">
         <v>35597</v>
       </c>
-      <c r="B502" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35597</v>
+      <c r="B502" s="4" t="s">
+        <v>1058</v>
       </c>
       <c r="C502" t="s">
         <v>515</v>
@@ -20193,9 +21346,8 @@
       <c r="A503" s="2">
         <v>35598</v>
       </c>
-      <c r="B503" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35598</v>
+      <c r="B503" t="s">
+        <v>1059</v>
       </c>
       <c r="C503" t="s">
         <v>493</v>
@@ -20229,9 +21381,8 @@
       <c r="A504" s="2">
         <v>35599</v>
       </c>
-      <c r="B504" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35599</v>
+      <c r="B504" s="4" t="s">
+        <v>1060</v>
       </c>
       <c r="C504" t="s">
         <v>493</v>
@@ -20265,9 +21416,8 @@
       <c r="A505" s="2">
         <v>35600</v>
       </c>
-      <c r="B505" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35600</v>
+      <c r="B505" t="s">
+        <v>1061</v>
       </c>
       <c r="C505" t="s">
         <v>493</v>
@@ -20301,9 +21451,8 @@
       <c r="A506" s="2">
         <v>35601</v>
       </c>
-      <c r="B506" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35601</v>
+      <c r="B506" s="4" t="s">
+        <v>1062</v>
       </c>
       <c r="C506" t="s">
         <v>516</v>
@@ -20337,9 +21486,8 @@
       <c r="A507" s="2">
         <v>35602</v>
       </c>
-      <c r="B507" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35602</v>
+      <c r="B507" t="s">
+        <v>1063</v>
       </c>
       <c r="C507" t="s">
         <v>517</v>
@@ -20373,9 +21521,8 @@
       <c r="A508" s="2">
         <v>35603</v>
       </c>
-      <c r="B508" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35603</v>
+      <c r="B508" s="4" t="s">
+        <v>1064</v>
       </c>
       <c r="C508" t="s">
         <v>493</v>
@@ -20409,9 +21556,8 @@
       <c r="A509" s="2">
         <v>35604</v>
       </c>
-      <c r="B509" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35604</v>
+      <c r="B509" t="s">
+        <v>1065</v>
       </c>
       <c r="C509" t="s">
         <v>493</v>
@@ -20445,9 +21591,8 @@
       <c r="A510" s="2">
         <v>35605</v>
       </c>
-      <c r="B510" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35605</v>
+      <c r="B510" s="4" t="s">
+        <v>1066</v>
       </c>
       <c r="C510" t="s">
         <v>493</v>
@@ -20481,9 +21626,8 @@
       <c r="A511" s="2">
         <v>35606</v>
       </c>
-      <c r="B511" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35606</v>
+      <c r="B511" t="s">
+        <v>1067</v>
       </c>
       <c r="C511" t="s">
         <v>493</v>
@@ -20517,9 +21661,8 @@
       <c r="A512" s="2">
         <v>35607</v>
       </c>
-      <c r="B512" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35607</v>
+      <c r="B512" s="4" t="s">
+        <v>1068</v>
       </c>
       <c r="C512" t="s">
         <v>493</v>
@@ -20553,9 +21696,8 @@
       <c r="A513" s="2">
         <v>35608</v>
       </c>
-      <c r="B513" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35608</v>
+      <c r="B513" t="s">
+        <v>1069</v>
       </c>
       <c r="C513" t="s">
         <v>518</v>
@@ -20589,9 +21731,8 @@
       <c r="A514" s="2">
         <v>35609</v>
       </c>
-      <c r="B514" t="str">
-        <f t="shared" si="7"/>
-        <v>Prchile-35609</v>
+      <c r="B514" s="4" t="s">
+        <v>1070</v>
       </c>
       <c r="C514" t="s">
         <v>493</v>
@@ -20625,9 +21766,8 @@
       <c r="A515" s="2">
         <v>35610</v>
       </c>
-      <c r="B515" t="str">
-        <f t="shared" ref="B515:B551" si="8">$B$1&amp;"-"&amp;A515</f>
-        <v>Prchile-35610</v>
+      <c r="B515" t="s">
+        <v>1071</v>
       </c>
       <c r="C515" t="s">
         <v>519</v>
@@ -20661,9 +21801,8 @@
       <c r="A516" s="2">
         <v>35611</v>
       </c>
-      <c r="B516" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35611</v>
+      <c r="B516" s="4" t="s">
+        <v>1072</v>
       </c>
       <c r="C516" t="s">
         <v>520</v>
@@ -20697,9 +21836,8 @@
       <c r="A517" s="2">
         <v>35612</v>
       </c>
-      <c r="B517" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35612</v>
+      <c r="B517" t="s">
+        <v>1073</v>
       </c>
       <c r="C517" t="s">
         <v>493</v>
@@ -20733,9 +21871,8 @@
       <c r="A518" s="2">
         <v>35613</v>
       </c>
-      <c r="B518" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35613</v>
+      <c r="B518" s="4" t="s">
+        <v>1074</v>
       </c>
       <c r="C518" t="s">
         <v>493</v>
@@ -20769,9 +21906,8 @@
       <c r="A519" s="2">
         <v>35614</v>
       </c>
-      <c r="B519" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35614</v>
+      <c r="B519" t="s">
+        <v>1075</v>
       </c>
       <c r="C519" t="s">
         <v>521</v>
@@ -20805,9 +21941,8 @@
       <c r="A520" s="2">
         <v>35615</v>
       </c>
-      <c r="B520" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35615</v>
+      <c r="B520" s="4" t="s">
+        <v>1076</v>
       </c>
       <c r="C520" t="s">
         <v>522</v>
@@ -20841,9 +21976,8 @@
       <c r="A521" s="2">
         <v>35616</v>
       </c>
-      <c r="B521" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35616</v>
+      <c r="B521" t="s">
+        <v>1077</v>
       </c>
       <c r="C521" t="s">
         <v>523</v>
@@ -20877,9 +22011,8 @@
       <c r="A522" s="2">
         <v>35617</v>
       </c>
-      <c r="B522" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35617</v>
+      <c r="B522" s="4" t="s">
+        <v>1078</v>
       </c>
       <c r="C522" t="s">
         <v>524</v>
@@ -20913,9 +22046,8 @@
       <c r="A523" s="2">
         <v>35618</v>
       </c>
-      <c r="B523" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35618</v>
+      <c r="B523" t="s">
+        <v>1079</v>
       </c>
       <c r="C523" t="s">
         <v>525</v>
@@ -20949,9 +22081,8 @@
       <c r="A524" s="2">
         <v>35619</v>
       </c>
-      <c r="B524" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35619</v>
+      <c r="B524" s="4" t="s">
+        <v>1080</v>
       </c>
       <c r="C524" t="s">
         <v>526</v>
@@ -20985,9 +22116,8 @@
       <c r="A525" s="2">
         <v>35620</v>
       </c>
-      <c r="B525" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35620</v>
+      <c r="B525" t="s">
+        <v>1081</v>
       </c>
       <c r="C525" t="s">
         <v>527</v>
@@ -21021,9 +22151,8 @@
       <c r="A526" s="2">
         <v>35621</v>
       </c>
-      <c r="B526" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35621</v>
+      <c r="B526" s="4" t="s">
+        <v>1082</v>
       </c>
       <c r="C526" t="s">
         <v>528</v>
@@ -21057,9 +22186,8 @@
       <c r="A527" s="2">
         <v>35622</v>
       </c>
-      <c r="B527" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35622</v>
+      <c r="B527" t="s">
+        <v>1083</v>
       </c>
       <c r="C527" t="s">
         <v>529</v>
@@ -21093,9 +22221,8 @@
       <c r="A528" s="2">
         <v>35623</v>
       </c>
-      <c r="B528" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35623</v>
+      <c r="B528" s="4" t="s">
+        <v>1084</v>
       </c>
       <c r="C528" t="s">
         <v>530</v>
@@ -21129,9 +22256,8 @@
       <c r="A529" s="2">
         <v>35624</v>
       </c>
-      <c r="B529" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35624</v>
+      <c r="B529" t="s">
+        <v>1085</v>
       </c>
       <c r="C529" t="s">
         <v>531</v>
@@ -21165,9 +22291,8 @@
       <c r="A530" s="2">
         <v>35625</v>
       </c>
-      <c r="B530" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35625</v>
+      <c r="B530" s="4" t="s">
+        <v>1086</v>
       </c>
       <c r="C530" t="s">
         <v>532</v>
@@ -21201,9 +22326,8 @@
       <c r="A531" s="2">
         <v>35626</v>
       </c>
-      <c r="B531" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35626</v>
+      <c r="B531" t="s">
+        <v>1087</v>
       </c>
       <c r="C531" t="s">
         <v>533</v>
@@ -21237,9 +22361,8 @@
       <c r="A532" s="2">
         <v>35627</v>
       </c>
-      <c r="B532" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35627</v>
+      <c r="B532" s="4" t="s">
+        <v>1088</v>
       </c>
       <c r="C532" t="s">
         <v>534</v>
@@ -21273,9 +22396,8 @@
       <c r="A533" s="2">
         <v>35628</v>
       </c>
-      <c r="B533" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35628</v>
+      <c r="B533" t="s">
+        <v>1089</v>
       </c>
       <c r="C533" t="s">
         <v>536</v>
@@ -21309,9 +22431,8 @@
       <c r="A534" s="2">
         <v>35629</v>
       </c>
-      <c r="B534" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35629</v>
+      <c r="B534" s="4" t="s">
+        <v>1090</v>
       </c>
       <c r="C534" t="s">
         <v>537</v>
@@ -21345,9 +22466,8 @@
       <c r="A535" s="2">
         <v>35630</v>
       </c>
-      <c r="B535" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35630</v>
+      <c r="B535" t="s">
+        <v>1091</v>
       </c>
       <c r="C535" t="s">
         <v>538</v>
@@ -21381,9 +22501,8 @@
       <c r="A536" s="2">
         <v>35631</v>
       </c>
-      <c r="B536" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35631</v>
+      <c r="B536" s="4" t="s">
+        <v>1092</v>
       </c>
       <c r="C536" t="s">
         <v>539</v>
@@ -21417,9 +22536,8 @@
       <c r="A537" s="2">
         <v>35632</v>
       </c>
-      <c r="B537" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35632</v>
+      <c r="B537" t="s">
+        <v>1093</v>
       </c>
       <c r="C537" t="s">
         <v>540</v>
@@ -21453,9 +22571,8 @@
       <c r="A538" s="2">
         <v>35633</v>
       </c>
-      <c r="B538" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35633</v>
+      <c r="B538" s="4" t="s">
+        <v>1094</v>
       </c>
       <c r="C538" t="s">
         <v>541</v>
@@ -21489,9 +22606,8 @@
       <c r="A539" s="2">
         <v>35634</v>
       </c>
-      <c r="B539" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35634</v>
+      <c r="B539" t="s">
+        <v>1095</v>
       </c>
       <c r="C539" t="s">
         <v>542</v>
@@ -21525,9 +22641,8 @@
       <c r="A540" s="2">
         <v>35635</v>
       </c>
-      <c r="B540" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35635</v>
+      <c r="B540" s="4" t="s">
+        <v>1096</v>
       </c>
       <c r="C540" t="s">
         <v>543</v>
@@ -21561,9 +22676,8 @@
       <c r="A541" s="2">
         <v>35636</v>
       </c>
-      <c r="B541" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35636</v>
+      <c r="B541" t="s">
+        <v>1097</v>
       </c>
       <c r="C541" t="s">
         <v>544</v>
@@ -21597,9 +22711,8 @@
       <c r="A542" s="2">
         <v>35637</v>
       </c>
-      <c r="B542" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35637</v>
+      <c r="B542" s="4" t="s">
+        <v>1098</v>
       </c>
       <c r="C542" t="s">
         <v>545</v>
@@ -21633,9 +22746,8 @@
       <c r="A543" s="2">
         <v>35638</v>
       </c>
-      <c r="B543" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35638</v>
+      <c r="B543" t="s">
+        <v>1099</v>
       </c>
       <c r="C543" t="s">
         <v>546</v>
@@ -21669,9 +22781,8 @@
       <c r="A544" s="2">
         <v>35639</v>
       </c>
-      <c r="B544" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35639</v>
+      <c r="B544" s="4" t="s">
+        <v>1100</v>
       </c>
       <c r="C544" t="s">
         <v>547</v>
@@ -21705,9 +22816,8 @@
       <c r="A545" s="2">
         <v>35640</v>
       </c>
-      <c r="B545" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35640</v>
+      <c r="B545" t="s">
+        <v>1101</v>
       </c>
       <c r="C545" t="s">
         <v>548</v>
@@ -21741,9 +22851,8 @@
       <c r="A546" s="2">
         <v>35641</v>
       </c>
-      <c r="B546" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35641</v>
+      <c r="B546" s="4" t="s">
+        <v>1102</v>
       </c>
       <c r="C546" t="s">
         <v>549</v>
@@ -21777,9 +22886,8 @@
       <c r="A547" s="2">
         <v>35642</v>
       </c>
-      <c r="B547" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35642</v>
+      <c r="B547" t="s">
+        <v>1103</v>
       </c>
       <c r="C547" t="s">
         <v>550</v>
@@ -21813,9 +22921,8 @@
       <c r="A548" s="2">
         <v>35643</v>
       </c>
-      <c r="B548" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35643</v>
+      <c r="B548" s="4" t="s">
+        <v>1104</v>
       </c>
       <c r="C548" t="s">
         <v>551</v>
@@ -21849,9 +22956,8 @@
       <c r="A549" s="2">
         <v>35644</v>
       </c>
-      <c r="B549" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35644</v>
+      <c r="B549" t="s">
+        <v>1105</v>
       </c>
       <c r="C549" t="s">
         <v>552</v>
@@ -21885,9 +22991,8 @@
       <c r="A550" s="2">
         <v>35645</v>
       </c>
-      <c r="B550" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35645</v>
+      <c r="B550" s="4" t="s">
+        <v>1106</v>
       </c>
       <c r="C550" t="s">
         <v>553</v>
@@ -21921,9 +23026,8 @@
       <c r="A551" s="2">
         <v>35646</v>
       </c>
-      <c r="B551" t="str">
-        <f t="shared" si="8"/>
-        <v>Prchile-35646</v>
+      <c r="B551" t="s">
+        <v>1107</v>
       </c>
       <c r="C551" t="s">
         <v>554</v>
